--- a/Моделирование ИАС/2 семестр/Пр4/Экспертные таблицы.xlsx
+++ b/Моделирование ИАС/2 семестр/Пр4/Экспертные таблицы.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\University\Моделирование ИАС\2 семестр\Пр4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\University\Моделирование ИАС\2 семестр\Пр4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{621D2294-724C-419C-B6FC-9B2AC0559CB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD35B3D4-D739-40C1-AAEE-1F974FC7A9A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="13680" xr2:uid="{179DB09E-B515-4FAE-BC6F-B4089FFA0642}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{179DB09E-B515-4FAE-BC6F-B4089FFA0642}"/>
   </bookViews>
   <sheets>
     <sheet name="Список угроз" sheetId="1" r:id="rId1"/>
@@ -511,9 +511,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
@@ -521,10 +518,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -840,16 +840,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2B8F044-46EB-409A-9153-D3EAF7757CCE}">
   <dimension ref="A1:G26"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="65.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="136.90625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="30.26953125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="65.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="136.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -872,7 +872,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -895,7 +895,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -918,7 +918,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -941,7 +941,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -964,7 +964,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -987,7 +987,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1010,7 +1010,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1033,7 +1033,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1056,7 +1056,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -1102,7 +1102,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -1125,7 +1125,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -1148,7 +1148,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -1171,7 +1171,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -1194,7 +1194,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -1217,7 +1217,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -1240,7 +1240,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -1263,7 +1263,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -1286,7 +1286,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -1309,7 +1309,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -1332,7 +1332,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -1355,7 +1355,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -1378,7 +1378,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -1401,7 +1401,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -1424,7 +1424,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -1455,44 +1455,44 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D64FF9B-855A-47AC-9E54-C709440D67DC}">
   <dimension ref="A1:P83"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="80.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="170.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="80.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="170.5546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.08984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="80.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="11.90625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="80.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.109375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="22" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.90625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.90625" customWidth="1"/>
-    <col min="15" max="15" width="12.6328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.88671875" customWidth="1"/>
+    <col min="15" max="15" width="12.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="18" x14ac:dyDescent="0.4">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:16" ht="18" x14ac:dyDescent="0.35">
+      <c r="A1" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="F1" s="5" t="s">
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="F1" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
       <c r="N1" s="4"/>
       <c r="O1" s="4"/>
       <c r="P1" s="4"/>
     </row>
-    <row r="2" spans="1:16" ht="18" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:16" ht="18" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -1505,32 +1505,32 @@
       <c r="D2" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="F2" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="G2" s="7" t="s">
+      <c r="F2" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="I2" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="J2" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="K2" s="7" t="s">
+      <c r="K2" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="L2" s="7" t="s">
+      <c r="L2" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="M2" s="7" t="s">
+      <c r="M2" s="6" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="18" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:16" ht="18" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -1543,33 +1543,33 @@
       <c r="D3" s="3">
         <v>9</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="6">
         <v>5</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="7">
+      <c r="H3" s="6">
         <v>9</v>
       </c>
-      <c r="I3" s="7">
+      <c r="I3" s="6">
         <v>8</v>
       </c>
-      <c r="J3" s="7">
+      <c r="J3" s="6">
         <v>9</v>
       </c>
-      <c r="K3" s="8">
+      <c r="K3" s="7">
         <f>AVERAGE(H3:J3)</f>
         <v>8.6666666666666661</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="L3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="M3" s="7">
+      <c r="M3" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="18" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:16" ht="18" x14ac:dyDescent="0.35">
       <c r="A4" s="3">
         <v>2</v>
       </c>
@@ -1582,33 +1582,33 @@
       <c r="D4" s="3">
         <v>8</v>
       </c>
-      <c r="F4" s="7">
-        <v>2</v>
-      </c>
-      <c r="G4" s="7" t="s">
+      <c r="F4" s="6">
+        <v>2</v>
+      </c>
+      <c r="G4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="H4" s="7">
+      <c r="H4" s="6">
         <v>8</v>
       </c>
-      <c r="I4" s="7">
+      <c r="I4" s="6">
         <v>9</v>
       </c>
-      <c r="J4" s="7">
+      <c r="J4" s="6">
         <v>8</v>
       </c>
-      <c r="K4" s="8">
+      <c r="K4" s="7">
         <f t="shared" ref="K4:K27" si="0">AVERAGE(H4:J4)</f>
         <v>8.3333333333333339</v>
       </c>
-      <c r="L4" s="7" t="s">
+      <c r="L4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="M4" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" ht="18" x14ac:dyDescent="0.4">
+      <c r="M4" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="18" x14ac:dyDescent="0.35">
       <c r="A5" s="3">
         <v>3</v>
       </c>
@@ -1621,33 +1621,33 @@
       <c r="D5" s="3">
         <v>7</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="6">
         <v>6</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="G5" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H5" s="6">
         <v>9</v>
       </c>
-      <c r="I5" s="7">
+      <c r="I5" s="6">
         <v>8</v>
       </c>
-      <c r="J5" s="7">
+      <c r="J5" s="6">
         <v>8</v>
       </c>
-      <c r="K5" s="8">
+      <c r="K5" s="7">
         <f t="shared" si="0"/>
         <v>8.3333333333333339</v>
       </c>
-      <c r="L5" s="7" t="s">
+      <c r="L5" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="M5" s="7">
+      <c r="M5" s="6">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="18" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:16" ht="18" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>4</v>
       </c>
@@ -1660,33 +1660,33 @@
       <c r="D6" s="3">
         <v>8</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="6">
         <v>19</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="H6" s="7">
+      <c r="H6" s="6">
         <v>9</v>
       </c>
-      <c r="I6" s="7">
+      <c r="I6" s="6">
         <v>8</v>
       </c>
-      <c r="J6" s="7">
+      <c r="J6" s="6">
         <v>8</v>
       </c>
-      <c r="K6" s="8">
+      <c r="K6" s="7">
         <f t="shared" si="0"/>
         <v>8.3333333333333339</v>
       </c>
-      <c r="L6" s="7" t="s">
+      <c r="L6" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="M6" s="7">
+      <c r="M6" s="6">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="18" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:16" ht="18" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>5</v>
       </c>
@@ -1699,33 +1699,33 @@
       <c r="D7" s="3">
         <v>9</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="6">
         <v>1</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="G7" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="H7" s="7">
+      <c r="H7" s="6">
         <v>9</v>
       </c>
-      <c r="I7" s="7">
+      <c r="I7" s="6">
         <v>8</v>
       </c>
-      <c r="J7" s="7">
+      <c r="J7" s="6">
         <v>7</v>
       </c>
-      <c r="K7" s="8">
+      <c r="K7" s="7">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="L7" s="7" t="s">
+      <c r="L7" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="M7" s="7">
+      <c r="M7" s="6">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="18" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:16" ht="18" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>6</v>
       </c>
@@ -1738,33 +1738,33 @@
       <c r="D8" s="3">
         <v>9</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="6">
         <v>3</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="G8" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="H8" s="7">
+      <c r="H8" s="6">
         <v>7</v>
       </c>
-      <c r="I8" s="7">
+      <c r="I8" s="6">
         <v>9</v>
       </c>
-      <c r="J8" s="7">
+      <c r="J8" s="6">
         <v>8</v>
       </c>
-      <c r="K8" s="8">
+      <c r="K8" s="7">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="L8" s="7" t="s">
+      <c r="L8" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="M8" s="7">
+      <c r="M8" s="6">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="18" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:16" ht="18" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>7</v>
       </c>
@@ -1777,33 +1777,33 @@
       <c r="D9" s="3">
         <v>7</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="6">
         <v>12</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="G9" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="H9" s="7">
+      <c r="H9" s="6">
         <v>8</v>
       </c>
-      <c r="I9" s="7">
+      <c r="I9" s="6">
         <v>8</v>
       </c>
-      <c r="J9" s="7">
+      <c r="J9" s="6">
         <v>8</v>
       </c>
-      <c r="K9" s="8">
+      <c r="K9" s="7">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="L9" s="7" t="s">
+      <c r="L9" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="M9" s="7">
+      <c r="M9" s="6">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="18" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:16" ht="18" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>8</v>
       </c>
@@ -1816,33 +1816,33 @@
       <c r="D10" s="3">
         <v>6</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="6">
         <v>17</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="G10" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="H10" s="7">
+      <c r="H10" s="6">
         <v>8</v>
       </c>
-      <c r="I10" s="7">
+      <c r="I10" s="6">
         <v>8</v>
       </c>
-      <c r="J10" s="7">
+      <c r="J10" s="6">
         <v>8</v>
       </c>
-      <c r="K10" s="8">
+      <c r="K10" s="7">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="L10" s="7" t="s">
+      <c r="L10" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="M10" s="7">
+      <c r="M10" s="6">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="18" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:16" ht="18" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>9</v>
       </c>
@@ -1855,33 +1855,33 @@
       <c r="D11" s="3">
         <v>5</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="6">
         <v>24</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="G11" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="H11" s="7">
+      <c r="H11" s="6">
         <v>8</v>
       </c>
-      <c r="I11" s="7">
+      <c r="I11" s="6">
         <v>8</v>
       </c>
-      <c r="J11" s="7">
+      <c r="J11" s="6">
         <v>7</v>
       </c>
-      <c r="K11" s="8">
+      <c r="K11" s="7">
         <f t="shared" si="0"/>
         <v>7.666666666666667</v>
       </c>
-      <c r="L11" s="7" t="s">
+      <c r="L11" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="M11" s="7">
+      <c r="M11" s="6">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="18" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:16" ht="18" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>10</v>
       </c>
@@ -1894,33 +1894,33 @@
       <c r="D12" s="3">
         <v>8</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="6">
         <v>4</v>
       </c>
-      <c r="G12" s="7" t="s">
+      <c r="G12" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H12" s="7">
+      <c r="H12" s="6">
         <v>8</v>
       </c>
-      <c r="I12" s="7">
+      <c r="I12" s="6">
         <v>7</v>
       </c>
-      <c r="J12" s="7">
+      <c r="J12" s="6">
         <v>7</v>
       </c>
-      <c r="K12" s="8">
+      <c r="K12" s="7">
         <f t="shared" si="0"/>
         <v>7.333333333333333</v>
       </c>
-      <c r="L12" s="7" t="s">
+      <c r="L12" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="M12" s="7">
+      <c r="M12" s="6">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="18" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:16" ht="18" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>11</v>
       </c>
@@ -1933,33 +1933,33 @@
       <c r="D13" s="3">
         <v>4</v>
       </c>
-      <c r="F13" s="7">
+      <c r="F13" s="6">
         <v>7</v>
       </c>
-      <c r="G13" s="7" t="s">
+      <c r="G13" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H13" s="7">
+      <c r="H13" s="6">
         <v>7</v>
       </c>
-      <c r="I13" s="7">
+      <c r="I13" s="6">
         <v>8</v>
       </c>
-      <c r="J13" s="7">
+      <c r="J13" s="6">
         <v>7</v>
       </c>
-      <c r="K13" s="8">
+      <c r="K13" s="7">
         <f t="shared" si="0"/>
         <v>7.333333333333333</v>
       </c>
-      <c r="L13" s="7" t="s">
+      <c r="L13" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="M13" s="7">
+      <c r="M13" s="6">
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="18" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:16" ht="18" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>12</v>
       </c>
@@ -1972,33 +1972,33 @@
       <c r="D14" s="3">
         <v>8</v>
       </c>
-      <c r="F14" s="7">
+      <c r="F14" s="6">
         <v>10</v>
       </c>
-      <c r="G14" s="7" t="s">
+      <c r="G14" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="H14" s="7">
+      <c r="H14" s="6">
         <v>8</v>
       </c>
-      <c r="I14" s="7">
+      <c r="I14" s="6">
         <v>7</v>
       </c>
-      <c r="J14" s="7">
+      <c r="J14" s="6">
         <v>7</v>
       </c>
-      <c r="K14" s="8">
+      <c r="K14" s="7">
         <f t="shared" si="0"/>
         <v>7.333333333333333</v>
       </c>
-      <c r="L14" s="7" t="s">
+      <c r="L14" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="M14" s="7">
+      <c r="M14" s="6">
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="18" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:16" ht="18" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>13</v>
       </c>
@@ -2011,33 +2011,33 @@
       <c r="D15" s="3">
         <v>7</v>
       </c>
-      <c r="F15" s="7">
+      <c r="F15" s="6">
         <v>21</v>
       </c>
-      <c r="G15" s="7" t="s">
+      <c r="G15" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="H15" s="7">
+      <c r="H15" s="6">
         <v>7</v>
       </c>
-      <c r="I15" s="7">
+      <c r="I15" s="6">
         <v>7</v>
       </c>
-      <c r="J15" s="7">
+      <c r="J15" s="6">
         <v>7</v>
       </c>
-      <c r="K15" s="8">
+      <c r="K15" s="7">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="L15" s="7" t="s">
+      <c r="L15" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M15" s="7">
+      <c r="M15" s="6">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="18" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:16" ht="18" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <v>14</v>
       </c>
@@ -2050,33 +2050,33 @@
       <c r="D16" s="3">
         <v>6</v>
       </c>
-      <c r="F16" s="7">
+      <c r="F16" s="6">
         <v>18</v>
       </c>
-      <c r="G16" s="7" t="s">
+      <c r="G16" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="H16" s="7">
+      <c r="H16" s="6">
         <v>7</v>
       </c>
-      <c r="I16" s="7">
+      <c r="I16" s="6">
         <v>7</v>
       </c>
-      <c r="J16" s="7">
+      <c r="J16" s="6">
         <v>6</v>
       </c>
-      <c r="K16" s="8">
+      <c r="K16" s="7">
         <f t="shared" si="0"/>
         <v>6.666666666666667</v>
       </c>
-      <c r="L16" s="7" t="s">
+      <c r="L16" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M16" s="7">
+      <c r="M16" s="6">
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="18" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:13" ht="18" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
         <v>15</v>
       </c>
@@ -2089,33 +2089,33 @@
       <c r="D17" s="3">
         <v>5</v>
       </c>
-      <c r="F17" s="7">
+      <c r="F17" s="6">
         <v>9</v>
       </c>
-      <c r="G17" s="7" t="s">
+      <c r="G17" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="H17" s="7">
+      <c r="H17" s="6">
         <v>5</v>
       </c>
-      <c r="I17" s="7">
+      <c r="I17" s="6">
         <v>8</v>
       </c>
-      <c r="J17" s="7">
+      <c r="J17" s="6">
         <v>6</v>
       </c>
-      <c r="K17" s="8">
+      <c r="K17" s="7">
         <f t="shared" si="0"/>
         <v>6.333333333333333</v>
       </c>
-      <c r="L17" s="7" t="s">
+      <c r="L17" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M17" s="7">
+      <c r="M17" s="6">
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="18" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:13" ht="18" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <v>16</v>
       </c>
@@ -2128,33 +2128,33 @@
       <c r="D18" s="3">
         <v>6</v>
       </c>
-      <c r="F18" s="7">
+      <c r="F18" s="6">
         <v>13</v>
       </c>
-      <c r="G18" s="7" t="s">
+      <c r="G18" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="H18" s="7">
+      <c r="H18" s="6">
         <v>7</v>
       </c>
-      <c r="I18" s="7">
+      <c r="I18" s="6">
         <v>6</v>
       </c>
-      <c r="J18" s="7">
+      <c r="J18" s="6">
         <v>6</v>
       </c>
-      <c r="K18" s="8">
+      <c r="K18" s="7">
         <f t="shared" si="0"/>
         <v>6.333333333333333</v>
       </c>
-      <c r="L18" s="7" t="s">
+      <c r="L18" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M18" s="7">
+      <c r="M18" s="6">
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="18" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:13" ht="18" x14ac:dyDescent="0.35">
       <c r="A19" s="3">
         <v>17</v>
       </c>
@@ -2167,33 +2167,33 @@
       <c r="D19" s="3">
         <v>8</v>
       </c>
-      <c r="F19" s="7">
+      <c r="F19" s="6">
         <v>14</v>
       </c>
-      <c r="G19" s="7" t="s">
+      <c r="G19" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="H19" s="7">
+      <c r="H19" s="6">
         <v>6</v>
       </c>
-      <c r="I19" s="7">
+      <c r="I19" s="6">
         <v>7</v>
       </c>
-      <c r="J19" s="7">
+      <c r="J19" s="6">
         <v>6</v>
       </c>
-      <c r="K19" s="8">
+      <c r="K19" s="7">
         <f t="shared" si="0"/>
         <v>6.333333333333333</v>
       </c>
-      <c r="L19" s="7" t="s">
+      <c r="L19" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M19" s="7">
+      <c r="M19" s="6">
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="18" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:13" ht="18" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
         <v>18</v>
       </c>
@@ -2206,33 +2206,33 @@
       <c r="D20" s="3">
         <v>7</v>
       </c>
-      <c r="F20" s="7">
+      <c r="F20" s="6">
         <v>22</v>
       </c>
-      <c r="G20" s="7" t="s">
+      <c r="G20" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="H20" s="7">
+      <c r="H20" s="6">
         <v>6</v>
       </c>
-      <c r="I20" s="7">
+      <c r="I20" s="6">
         <v>7</v>
       </c>
-      <c r="J20" s="7">
+      <c r="J20" s="6">
         <v>6</v>
       </c>
-      <c r="K20" s="8">
+      <c r="K20" s="7">
         <f t="shared" si="0"/>
         <v>6.333333333333333</v>
       </c>
-      <c r="L20" s="7" t="s">
+      <c r="L20" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M20" s="7">
+      <c r="M20" s="6">
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="18" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:13" ht="18" x14ac:dyDescent="0.35">
       <c r="A21" s="3">
         <v>19</v>
       </c>
@@ -2245,33 +2245,33 @@
       <c r="D21" s="3">
         <v>9</v>
       </c>
-      <c r="F21" s="7">
+      <c r="F21" s="6">
         <v>25</v>
       </c>
-      <c r="G21" s="7" t="s">
+      <c r="G21" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="H21" s="7">
+      <c r="H21" s="6">
         <v>7</v>
       </c>
-      <c r="I21" s="7">
+      <c r="I21" s="6">
         <v>6</v>
       </c>
-      <c r="J21" s="7">
+      <c r="J21" s="6">
         <v>6</v>
       </c>
-      <c r="K21" s="8">
+      <c r="K21" s="7">
         <f t="shared" si="0"/>
         <v>6.333333333333333</v>
       </c>
-      <c r="L21" s="7" t="s">
+      <c r="L21" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M21" s="7">
+      <c r="M21" s="6">
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="18" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:13" ht="18" x14ac:dyDescent="0.35">
       <c r="A22" s="3">
         <v>20</v>
       </c>
@@ -2284,33 +2284,33 @@
       <c r="D22" s="3">
         <v>5</v>
       </c>
-      <c r="F22" s="7">
+      <c r="F22" s="6">
         <v>16</v>
       </c>
-      <c r="G22" s="7" t="s">
+      <c r="G22" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="H22" s="7">
+      <c r="H22" s="6">
         <v>6</v>
       </c>
-      <c r="I22" s="7">
+      <c r="I22" s="6">
         <v>6</v>
       </c>
-      <c r="J22" s="7">
+      <c r="J22" s="6">
         <v>5</v>
       </c>
-      <c r="K22" s="8">
+      <c r="K22" s="7">
         <f t="shared" si="0"/>
         <v>5.666666666666667</v>
       </c>
-      <c r="L22" s="7" t="s">
+      <c r="L22" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M22" s="7">
+      <c r="M22" s="6">
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="18" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:13" ht="18" x14ac:dyDescent="0.35">
       <c r="A23" s="3">
         <v>21</v>
       </c>
@@ -2323,33 +2323,33 @@
       <c r="D23" s="3">
         <v>7</v>
       </c>
-      <c r="F23" s="7">
+      <c r="F23" s="6">
         <v>8</v>
       </c>
-      <c r="G23" s="7" t="s">
+      <c r="G23" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="H23" s="7">
+      <c r="H23" s="6">
         <v>6</v>
       </c>
-      <c r="I23" s="7">
+      <c r="I23" s="6">
         <v>5</v>
       </c>
-      <c r="J23" s="7">
+      <c r="J23" s="6">
         <v>5</v>
       </c>
-      <c r="K23" s="8">
+      <c r="K23" s="7">
         <f t="shared" si="0"/>
         <v>5.333333333333333</v>
       </c>
-      <c r="L23" s="7" t="s">
+      <c r="L23" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M23" s="7">
+      <c r="M23" s="6">
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="18" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:13" ht="18" x14ac:dyDescent="0.35">
       <c r="A24" s="3">
         <v>22</v>
       </c>
@@ -2362,33 +2362,33 @@
       <c r="D24" s="3">
         <v>6</v>
       </c>
-      <c r="F24" s="7">
+      <c r="F24" s="6">
         <v>11</v>
       </c>
-      <c r="G24" s="7" t="s">
+      <c r="G24" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="H24" s="7">
+      <c r="H24" s="6">
         <v>4</v>
       </c>
-      <c r="I24" s="7">
+      <c r="I24" s="6">
         <v>7</v>
       </c>
-      <c r="J24" s="7">
+      <c r="J24" s="6">
         <v>5</v>
       </c>
-      <c r="K24" s="8">
+      <c r="K24" s="7">
         <f t="shared" si="0"/>
         <v>5.333333333333333</v>
       </c>
-      <c r="L24" s="7" t="s">
+      <c r="L24" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M24" s="7">
+      <c r="M24" s="6">
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="18" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:13" ht="18" x14ac:dyDescent="0.35">
       <c r="A25" s="3">
         <v>23</v>
       </c>
@@ -2401,33 +2401,33 @@
       <c r="D25" s="3">
         <v>5</v>
       </c>
-      <c r="F25" s="7">
+      <c r="F25" s="6">
         <v>15</v>
       </c>
-      <c r="G25" s="7" t="s">
+      <c r="G25" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="H25" s="7">
+      <c r="H25" s="6">
         <v>5</v>
       </c>
-      <c r="I25" s="7">
+      <c r="I25" s="6">
         <v>6</v>
       </c>
-      <c r="J25" s="7">
+      <c r="J25" s="6">
         <v>5</v>
       </c>
-      <c r="K25" s="8">
+      <c r="K25" s="7">
         <f t="shared" si="0"/>
         <v>5.333333333333333</v>
       </c>
-      <c r="L25" s="7" t="s">
+      <c r="L25" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M25" s="7">
+      <c r="M25" s="6">
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="18" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:13" ht="18" x14ac:dyDescent="0.35">
       <c r="A26" s="3">
         <v>24</v>
       </c>
@@ -2440,33 +2440,33 @@
       <c r="D26" s="3">
         <v>8</v>
       </c>
-      <c r="F26" s="7">
+      <c r="F26" s="6">
         <v>20</v>
       </c>
-      <c r="G26" s="7" t="s">
+      <c r="G26" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="H26" s="7">
+      <c r="H26" s="6">
         <v>5</v>
       </c>
-      <c r="I26" s="7">
+      <c r="I26" s="6">
         <v>6</v>
       </c>
-      <c r="J26" s="7">
+      <c r="J26" s="6">
         <v>5</v>
       </c>
-      <c r="K26" s="8">
+      <c r="K26" s="7">
         <f t="shared" si="0"/>
         <v>5.333333333333333</v>
       </c>
-      <c r="L26" s="7" t="s">
+      <c r="L26" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M26" s="7">
+      <c r="M26" s="6">
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="18" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:13" ht="18" x14ac:dyDescent="0.35">
       <c r="A27" s="3">
         <v>25</v>
       </c>
@@ -2479,41 +2479,41 @@
       <c r="D27" s="3">
         <v>7</v>
       </c>
-      <c r="F27" s="7">
+      <c r="F27" s="6">
         <v>23</v>
       </c>
-      <c r="G27" s="7" t="s">
+      <c r="G27" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="H27" s="7">
+      <c r="H27" s="6">
         <v>5</v>
       </c>
-      <c r="I27" s="7">
+      <c r="I27" s="6">
         <v>6</v>
       </c>
-      <c r="J27" s="7">
+      <c r="J27" s="6">
         <v>5</v>
       </c>
-      <c r="K27" s="8">
+      <c r="K27" s="7">
         <f t="shared" si="0"/>
         <v>5.333333333333333</v>
       </c>
-      <c r="L27" s="7" t="s">
+      <c r="L27" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M27" s="7">
+      <c r="M27" s="6">
         <v>25</v>
       </c>
     </row>
-    <row r="29" spans="1:13" ht="18" x14ac:dyDescent="0.4">
-      <c r="A29" s="5" t="s">
+    <row r="29" spans="1:13" ht="18" x14ac:dyDescent="0.35">
+      <c r="A29" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="B29" s="5"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
-    </row>
-    <row r="30" spans="1:13" ht="18" x14ac:dyDescent="0.4">
+      <c r="B29" s="10"/>
+      <c r="C29" s="10"/>
+      <c r="D29" s="10"/>
+    </row>
+    <row r="30" spans="1:13" ht="18" x14ac:dyDescent="0.35">
       <c r="A30" s="3" t="s">
         <v>0</v>
       </c>
@@ -2527,7 +2527,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="18" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:13" ht="18" x14ac:dyDescent="0.35">
       <c r="A31" s="3">
         <v>1</v>
       </c>
@@ -2541,7 +2541,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="18" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:13" ht="18" x14ac:dyDescent="0.35">
       <c r="A32" s="3">
         <v>2</v>
       </c>
@@ -2555,7 +2555,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="18" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A33" s="3">
         <v>3</v>
       </c>
@@ -2569,7 +2569,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="18" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A34" s="3">
         <v>4</v>
       </c>
@@ -2583,7 +2583,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="18" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A35" s="3">
         <v>5</v>
       </c>
@@ -2597,7 +2597,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="18" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A36" s="3">
         <v>6</v>
       </c>
@@ -2611,7 +2611,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="18" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A37" s="3">
         <v>7</v>
       </c>
@@ -2625,7 +2625,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="18" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A38" s="3">
         <v>8</v>
       </c>
@@ -2639,7 +2639,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="18" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A39" s="3">
         <v>9</v>
       </c>
@@ -2653,7 +2653,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="18" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A40" s="3">
         <v>10</v>
       </c>
@@ -2667,7 +2667,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="18" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A41" s="3">
         <v>11</v>
       </c>
@@ -2681,7 +2681,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="18" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A42" s="3">
         <v>12</v>
       </c>
@@ -2695,7 +2695,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="18" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A43" s="3">
         <v>13</v>
       </c>
@@ -2709,7 +2709,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="18" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A44" s="3">
         <v>14</v>
       </c>
@@ -2723,7 +2723,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="18" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A45" s="3">
         <v>15</v>
       </c>
@@ -2737,7 +2737,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="18" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A46" s="3">
         <v>16</v>
       </c>
@@ -2751,7 +2751,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="18" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A47" s="3">
         <v>17</v>
       </c>
@@ -2765,7 +2765,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="18" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A48" s="3">
         <v>18</v>
       </c>
@@ -2779,7 +2779,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="18" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A49" s="3">
         <v>19</v>
       </c>
@@ -2793,7 +2793,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="18" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A50" s="3">
         <v>20</v>
       </c>
@@ -2807,7 +2807,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="18" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A51" s="3">
         <v>21</v>
       </c>
@@ -2821,7 +2821,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="18" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A52" s="3">
         <v>22</v>
       </c>
@@ -2835,7 +2835,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="18" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A53" s="3">
         <v>23</v>
       </c>
@@ -2849,7 +2849,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="18" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A54" s="3">
         <v>24</v>
       </c>
@@ -2863,7 +2863,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="18" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A55" s="3">
         <v>25</v>
       </c>
@@ -2877,15 +2877,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="57" spans="1:4" ht="18" x14ac:dyDescent="0.4">
-      <c r="A57" s="5" t="s">
+    <row r="57" spans="1:4" ht="18" x14ac:dyDescent="0.35">
+      <c r="A57" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="B57" s="5"/>
-      <c r="C57" s="5"/>
-      <c r="D57" s="5"/>
-    </row>
-    <row r="58" spans="1:4" ht="18" x14ac:dyDescent="0.4">
+      <c r="B57" s="10"/>
+      <c r="C57" s="10"/>
+      <c r="D57" s="10"/>
+    </row>
+    <row r="58" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
         <v>0</v>
       </c>
@@ -2899,7 +2899,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="18" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A59" s="2">
         <v>1</v>
       </c>
@@ -2913,7 +2913,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="60" spans="1:4" ht="18" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A60" s="2">
         <v>2</v>
       </c>
@@ -2927,7 +2927,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="61" spans="1:4" ht="18" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A61" s="2">
         <v>3</v>
       </c>
@@ -2941,7 +2941,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="62" spans="1:4" ht="18" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A62" s="2">
         <v>4</v>
       </c>
@@ -2955,7 +2955,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="63" spans="1:4" ht="18" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A63" s="2">
         <v>5</v>
       </c>
@@ -2969,7 +2969,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="64" spans="1:4" ht="18" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A64" s="2">
         <v>6</v>
       </c>
@@ -2983,7 +2983,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="65" spans="1:4" ht="18" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A65" s="2">
         <v>7</v>
       </c>
@@ -2997,7 +2997,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="66" spans="1:4" ht="18" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A66" s="2">
         <v>8</v>
       </c>
@@ -3011,7 +3011,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="67" spans="1:4" ht="18" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A67" s="2">
         <v>9</v>
       </c>
@@ -3025,7 +3025,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="68" spans="1:4" ht="18" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A68" s="2">
         <v>10</v>
       </c>
@@ -3039,7 +3039,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="69" spans="1:4" ht="18" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A69" s="2">
         <v>11</v>
       </c>
@@ -3053,7 +3053,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="70" spans="1:4" ht="18" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A70" s="2">
         <v>12</v>
       </c>
@@ -3067,7 +3067,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="71" spans="1:4" ht="18" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A71" s="2">
         <v>13</v>
       </c>
@@ -3081,7 +3081,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="72" spans="1:4" ht="18" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A72" s="2">
         <v>14</v>
       </c>
@@ -3095,7 +3095,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="73" spans="1:4" ht="18" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A73" s="2">
         <v>15</v>
       </c>
@@ -3109,7 +3109,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="74" spans="1:4" ht="18" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A74" s="2">
         <v>16</v>
       </c>
@@ -3123,7 +3123,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="75" spans="1:4" ht="18" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A75" s="2">
         <v>17</v>
       </c>
@@ -3137,7 +3137,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="76" spans="1:4" ht="18" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A76" s="2">
         <v>18</v>
       </c>
@@ -3151,7 +3151,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="77" spans="1:4" ht="18" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A77" s="2">
         <v>19</v>
       </c>
@@ -3165,7 +3165,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="78" spans="1:4" ht="18" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A78" s="2">
         <v>20</v>
       </c>
@@ -3179,7 +3179,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="79" spans="1:4" ht="18" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A79" s="2">
         <v>21</v>
       </c>
@@ -3193,7 +3193,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="80" spans="1:4" ht="18" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A80" s="2">
         <v>22</v>
       </c>
@@ -3207,7 +3207,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="81" spans="1:4" ht="18" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A81" s="2">
         <v>23</v>
       </c>
@@ -3221,7 +3221,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="82" spans="1:4" ht="18" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A82" s="2">
         <v>24</v>
       </c>
@@ -3235,7 +3235,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="83" spans="1:4" ht="18" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A83" s="2">
         <v>25</v>
       </c>
@@ -3264,46 +3264,46 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B702145-23FF-4CA1-97C0-C4665B9AD674}">
   <dimension ref="A1:N83"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="80.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.08984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="80.90625" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="16.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="80.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="80.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="16.88671875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="16" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="22" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="5.90625" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="5.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="18" x14ac:dyDescent="0.4">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:14" ht="18" x14ac:dyDescent="0.35">
+      <c r="A1" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="E1" s="5" t="s">
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="E1" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
     </row>
-    <row r="2" spans="1:14" ht="18" x14ac:dyDescent="0.4">
-      <c r="A2" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="9" t="s">
+    <row r="2" spans="1:14" ht="18" x14ac:dyDescent="0.35">
+      <c r="A2" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="8" t="s">
         <v>76</v>
       </c>
       <c r="E2" s="3" t="s">
@@ -3333,14 +3333,14 @@
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
     </row>
-    <row r="3" spans="1:14" ht="18" x14ac:dyDescent="0.4">
-      <c r="A3" s="9">
+    <row r="3" spans="1:14" ht="18" x14ac:dyDescent="0.35">
+      <c r="A3" s="8">
         <v>6</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="9">
+      <c r="C3" s="8">
         <v>1</v>
       </c>
       <c r="E3" s="3">
@@ -3358,8 +3358,8 @@
       <c r="I3" s="3">
         <v>2</v>
       </c>
-      <c r="J3" s="11">
-        <f xml:space="preserve"> AVERAGE(G3:I3)</f>
+      <c r="J3" s="9">
+        <f t="shared" ref="J3:J27" si="0" xml:space="preserve"> AVERAGE(G3:I3)</f>
         <v>1.6666666666666667</v>
       </c>
       <c r="K3" s="3" t="s">
@@ -3371,14 +3371,14 @@
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
     </row>
-    <row r="4" spans="1:14" ht="18" x14ac:dyDescent="0.4">
-      <c r="A4" s="9">
+    <row r="4" spans="1:14" ht="18" x14ac:dyDescent="0.35">
+      <c r="A4" s="8">
         <v>5</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="9">
+      <c r="C4" s="8">
         <v>2</v>
       </c>
       <c r="E4" s="3">
@@ -3396,8 +3396,8 @@
       <c r="I4" s="3">
         <v>1</v>
       </c>
-      <c r="J4" s="11">
-        <f xml:space="preserve"> AVERAGE(G4:I4)</f>
+      <c r="J4" s="9">
+        <f t="shared" si="0"/>
         <v>2.3333333333333335</v>
       </c>
       <c r="K4" s="3" t="s">
@@ -3409,14 +3409,14 @@
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
     </row>
-    <row r="5" spans="1:14" ht="18" x14ac:dyDescent="0.4">
-      <c r="A5" s="9">
-        <v>2</v>
-      </c>
-      <c r="B5" s="9" t="s">
+    <row r="5" spans="1:14" ht="18" x14ac:dyDescent="0.35">
+      <c r="A5" s="8">
+        <v>2</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="8">
         <v>3</v>
       </c>
       <c r="E5" s="3">
@@ -3434,8 +3434,8 @@
       <c r="I5" s="3">
         <v>3</v>
       </c>
-      <c r="J5" s="11">
-        <f xml:space="preserve"> AVERAGE(G5:I5)</f>
+      <c r="J5" s="9">
+        <f t="shared" si="0"/>
         <v>2.6666666666666665</v>
       </c>
       <c r="K5" s="3" t="s">
@@ -3447,14 +3447,14 @@
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
     </row>
-    <row r="6" spans="1:14" ht="18" x14ac:dyDescent="0.4">
-      <c r="A6" s="9">
+    <row r="6" spans="1:14" ht="18" x14ac:dyDescent="0.35">
+      <c r="A6" s="8">
         <v>19</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="C6" s="9">
+      <c r="C6" s="8">
         <v>4</v>
       </c>
       <c r="E6" s="3">
@@ -3472,8 +3472,8 @@
       <c r="I6" s="3">
         <v>4</v>
       </c>
-      <c r="J6" s="11">
-        <f xml:space="preserve"> AVERAGE(G6:I6)</f>
+      <c r="J6" s="9">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="K6" s="3" t="s">
@@ -3485,14 +3485,14 @@
       <c r="M6" s="1"/>
       <c r="N6" s="1"/>
     </row>
-    <row r="7" spans="1:14" ht="18" x14ac:dyDescent="0.4">
-      <c r="A7" s="9">
+    <row r="7" spans="1:14" ht="18" x14ac:dyDescent="0.35">
+      <c r="A7" s="8">
         <v>1</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="9">
+      <c r="C7" s="8">
         <v>5</v>
       </c>
       <c r="E7" s="3">
@@ -3510,8 +3510,8 @@
       <c r="I7" s="3">
         <v>6</v>
       </c>
-      <c r="J7" s="11">
-        <f xml:space="preserve"> AVERAGE(G7:I7)</f>
+      <c r="J7" s="9">
+        <f t="shared" si="0"/>
         <v>4.666666666666667</v>
       </c>
       <c r="K7" s="3" t="s">
@@ -3523,14 +3523,14 @@
       <c r="M7" s="1"/>
       <c r="N7" s="1"/>
     </row>
-    <row r="8" spans="1:14" ht="18" x14ac:dyDescent="0.4">
-      <c r="A8" s="9">
+    <row r="8" spans="1:14" ht="18" x14ac:dyDescent="0.35">
+      <c r="A8" s="8">
         <v>3</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="9">
+      <c r="C8" s="8">
         <v>6</v>
       </c>
       <c r="E8" s="3">
@@ -3548,8 +3548,8 @@
       <c r="I8" s="3">
         <v>5</v>
       </c>
-      <c r="J8" s="11">
-        <f xml:space="preserve"> AVERAGE(G8:I8)</f>
+      <c r="J8" s="9">
+        <f t="shared" si="0"/>
         <v>5.666666666666667</v>
       </c>
       <c r="K8" s="3" t="s">
@@ -3561,14 +3561,14 @@
       <c r="M8" s="1"/>
       <c r="N8" s="1"/>
     </row>
-    <row r="9" spans="1:14" ht="18" x14ac:dyDescent="0.4">
-      <c r="A9" s="9">
+    <row r="9" spans="1:14" ht="18" x14ac:dyDescent="0.35">
+      <c r="A9" s="8">
         <v>17</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="C9" s="9">
+      <c r="C9" s="8">
         <v>7</v>
       </c>
       <c r="E9" s="3">
@@ -3586,8 +3586,8 @@
       <c r="I9" s="3">
         <v>8</v>
       </c>
-      <c r="J9" s="11">
-        <f xml:space="preserve"> AVERAGE(G9:I9)</f>
+      <c r="J9" s="9">
+        <f t="shared" si="0"/>
         <v>6.666666666666667</v>
       </c>
       <c r="K9" s="3" t="s">
@@ -3599,14 +3599,14 @@
       <c r="M9" s="1"/>
       <c r="N9" s="1"/>
     </row>
-    <row r="10" spans="1:14" ht="18" x14ac:dyDescent="0.4">
-      <c r="A10" s="9">
+    <row r="10" spans="1:14" ht="18" x14ac:dyDescent="0.35">
+      <c r="A10" s="8">
         <v>12</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="9">
+      <c r="C10" s="8">
         <v>8</v>
       </c>
       <c r="E10" s="3">
@@ -3624,8 +3624,8 @@
       <c r="I10" s="3">
         <v>7</v>
       </c>
-      <c r="J10" s="11">
-        <f xml:space="preserve"> AVERAGE(G10:I10)</f>
+      <c r="J10" s="9">
+        <f t="shared" si="0"/>
         <v>7.333333333333333</v>
       </c>
       <c r="K10" s="3" t="s">
@@ -3637,14 +3637,14 @@
       <c r="M10" s="1"/>
       <c r="N10" s="1"/>
     </row>
-    <row r="11" spans="1:14" ht="18" x14ac:dyDescent="0.4">
-      <c r="A11" s="9">
+    <row r="11" spans="1:14" ht="18" x14ac:dyDescent="0.35">
+      <c r="A11" s="8">
         <v>4</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="9">
+      <c r="C11" s="8">
         <v>9</v>
       </c>
       <c r="E11" s="3">
@@ -3662,8 +3662,8 @@
       <c r="I11" s="3">
         <v>9</v>
       </c>
-      <c r="J11" s="11">
-        <f xml:space="preserve"> AVERAGE(G11:I11)</f>
+      <c r="J11" s="9">
+        <f t="shared" si="0"/>
         <v>9.6666666666666661</v>
       </c>
       <c r="K11" s="3" t="s">
@@ -3675,14 +3675,14 @@
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
     </row>
-    <row r="12" spans="1:14" ht="18" x14ac:dyDescent="0.4">
-      <c r="A12" s="9">
+    <row r="12" spans="1:14" ht="18" x14ac:dyDescent="0.35">
+      <c r="A12" s="8">
         <v>24</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="C12" s="9">
+      <c r="C12" s="8">
         <v>10</v>
       </c>
       <c r="E12" s="3">
@@ -3700,8 +3700,8 @@
       <c r="I12" s="3">
         <v>10</v>
       </c>
-      <c r="J12" s="11">
-        <f xml:space="preserve"> AVERAGE(G12:I12)</f>
+      <c r="J12" s="9">
+        <f t="shared" si="0"/>
         <v>10.333333333333334</v>
       </c>
       <c r="K12" s="3" t="s">
@@ -3713,14 +3713,14 @@
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
     </row>
-    <row r="13" spans="1:14" ht="18" x14ac:dyDescent="0.4">
-      <c r="A13" s="9">
+    <row r="13" spans="1:14" ht="18" x14ac:dyDescent="0.35">
+      <c r="A13" s="8">
         <v>10</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="9">
+      <c r="C13" s="8">
         <v>11</v>
       </c>
       <c r="E13" s="3">
@@ -3738,8 +3738,8 @@
       <c r="I13" s="3">
         <v>11</v>
       </c>
-      <c r="J13" s="11">
-        <f xml:space="preserve"> AVERAGE(G13:I13)</f>
+      <c r="J13" s="9">
+        <f t="shared" si="0"/>
         <v>10.333333333333334</v>
       </c>
       <c r="K13" s="3" t="s">
@@ -3751,14 +3751,14 @@
       <c r="M13" s="1"/>
       <c r="N13" s="1"/>
     </row>
-    <row r="14" spans="1:14" ht="18" x14ac:dyDescent="0.4">
-      <c r="A14" s="9">
+    <row r="14" spans="1:14" ht="18" x14ac:dyDescent="0.35">
+      <c r="A14" s="8">
         <v>7</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="9">
+      <c r="C14" s="8">
         <v>12</v>
       </c>
       <c r="E14" s="3">
@@ -3776,8 +3776,8 @@
       <c r="I14" s="3">
         <v>12</v>
       </c>
-      <c r="J14" s="11">
-        <f xml:space="preserve"> AVERAGE(G14:I14)</f>
+      <c r="J14" s="9">
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="K14" s="3" t="s">
@@ -3789,14 +3789,14 @@
       <c r="M14" s="1"/>
       <c r="N14" s="1"/>
     </row>
-    <row r="15" spans="1:14" ht="18" x14ac:dyDescent="0.4">
-      <c r="A15" s="9">
+    <row r="15" spans="1:14" ht="18" x14ac:dyDescent="0.35">
+      <c r="A15" s="8">
         <v>21</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="C15" s="9">
+      <c r="C15" s="8">
         <v>13</v>
       </c>
       <c r="E15" s="3">
@@ -3814,8 +3814,8 @@
       <c r="I15" s="3">
         <v>14</v>
       </c>
-      <c r="J15" s="11">
-        <f xml:space="preserve"> AVERAGE(G15:I15)</f>
+      <c r="J15" s="9">
+        <f t="shared" si="0"/>
         <v>13.666666666666666</v>
       </c>
       <c r="K15" s="3" t="s">
@@ -3827,14 +3827,14 @@
       <c r="M15" s="1"/>
       <c r="N15" s="1"/>
     </row>
-    <row r="16" spans="1:14" ht="18" x14ac:dyDescent="0.4">
-      <c r="A16" s="9">
+    <row r="16" spans="1:14" ht="18" x14ac:dyDescent="0.35">
+      <c r="A16" s="8">
         <v>18</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="C16" s="9">
+      <c r="C16" s="8">
         <v>14</v>
       </c>
       <c r="E16" s="3">
@@ -3852,8 +3852,8 @@
       <c r="I16" s="3">
         <v>13</v>
       </c>
-      <c r="J16" s="11">
-        <f xml:space="preserve"> AVERAGE(G16:I16)</f>
+      <c r="J16" s="9">
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="K16" s="3" t="s">
@@ -3865,14 +3865,14 @@
       <c r="M16" s="1"/>
       <c r="N16" s="1"/>
     </row>
-    <row r="17" spans="1:14" ht="18" x14ac:dyDescent="0.4">
-      <c r="A17" s="9">
+    <row r="17" spans="1:14" ht="18" x14ac:dyDescent="0.35">
+      <c r="A17" s="8">
         <v>13</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="C17" s="9">
+      <c r="C17" s="8">
         <v>15</v>
       </c>
       <c r="E17" s="3">
@@ -3890,8 +3890,8 @@
       <c r="I17" s="3">
         <v>18</v>
       </c>
-      <c r="J17" s="11">
-        <f xml:space="preserve"> AVERAGE(G17:I17)</f>
+      <c r="J17" s="9">
+        <f t="shared" si="0"/>
         <v>15.333333333333334</v>
       </c>
       <c r="K17" s="3" t="s">
@@ -3903,14 +3903,14 @@
       <c r="M17" s="1"/>
       <c r="N17" s="1"/>
     </row>
-    <row r="18" spans="1:14" ht="18" x14ac:dyDescent="0.4">
-      <c r="A18" s="9">
+    <row r="18" spans="1:14" ht="18" x14ac:dyDescent="0.35">
+      <c r="A18" s="8">
         <v>9</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="C18" s="9">
+      <c r="C18" s="8">
         <v>16</v>
       </c>
       <c r="E18" s="3">
@@ -3928,8 +3928,8 @@
       <c r="I18" s="3">
         <v>15</v>
       </c>
-      <c r="J18" s="11">
-        <f xml:space="preserve"> AVERAGE(G18:I18)</f>
+      <c r="J18" s="9">
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="K18" s="3" t="s">
@@ -3941,14 +3941,14 @@
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
     </row>
-    <row r="19" spans="1:14" ht="18" x14ac:dyDescent="0.4">
-      <c r="A19" s="9">
+    <row r="19" spans="1:14" ht="18" x14ac:dyDescent="0.35">
+      <c r="A19" s="8">
         <v>14</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="C19" s="9">
+      <c r="C19" s="8">
         <v>17</v>
       </c>
       <c r="E19" s="3">
@@ -3966,8 +3966,8 @@
       <c r="I19" s="3">
         <v>16</v>
       </c>
-      <c r="J19" s="11">
-        <f xml:space="preserve"> AVERAGE(G19:I19)</f>
+      <c r="J19" s="9">
+        <f t="shared" si="0"/>
         <v>17.333333333333332</v>
       </c>
       <c r="K19" s="3" t="s">
@@ -3979,14 +3979,14 @@
       <c r="M19" s="1"/>
       <c r="N19" s="1"/>
     </row>
-    <row r="20" spans="1:14" ht="18" x14ac:dyDescent="0.4">
-      <c r="A20" s="9">
+    <row r="20" spans="1:14" ht="18" x14ac:dyDescent="0.35">
+      <c r="A20" s="8">
         <v>22</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="C20" s="9">
+      <c r="C20" s="8">
         <v>18</v>
       </c>
       <c r="E20" s="3">
@@ -4004,8 +4004,8 @@
       <c r="I20" s="3">
         <v>17</v>
       </c>
-      <c r="J20" s="11">
-        <f xml:space="preserve"> AVERAGE(G20:I20)</f>
+      <c r="J20" s="9">
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="K20" s="3" t="s">
@@ -4017,14 +4017,14 @@
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
     </row>
-    <row r="21" spans="1:14" ht="18" x14ac:dyDescent="0.4">
-      <c r="A21" s="9">
+    <row r="21" spans="1:14" ht="18" x14ac:dyDescent="0.35">
+      <c r="A21" s="8">
         <v>25</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="B21" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="C21" s="9">
+      <c r="C21" s="8">
         <v>19</v>
       </c>
       <c r="E21" s="3">
@@ -4042,8 +4042,8 @@
       <c r="I21" s="3">
         <v>19</v>
       </c>
-      <c r="J21" s="11">
-        <f xml:space="preserve"> AVERAGE(G21:I21)</f>
+      <c r="J21" s="9">
+        <f t="shared" si="0"/>
         <v>19.333333333333332</v>
       </c>
       <c r="K21" s="3" t="s">
@@ -4055,14 +4055,14 @@
       <c r="M21" s="1"/>
       <c r="N21" s="1"/>
     </row>
-    <row r="22" spans="1:14" ht="18" x14ac:dyDescent="0.4">
-      <c r="A22" s="9">
+    <row r="22" spans="1:14" ht="18" x14ac:dyDescent="0.35">
+      <c r="A22" s="8">
         <v>16</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="B22" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="C22" s="9">
+      <c r="C22" s="8">
         <v>20</v>
       </c>
       <c r="E22" s="3">
@@ -4080,8 +4080,8 @@
       <c r="I22" s="3">
         <v>20</v>
       </c>
-      <c r="J22" s="11">
-        <f xml:space="preserve"> AVERAGE(G22:I22)</f>
+      <c r="J22" s="9">
+        <f t="shared" si="0"/>
         <v>20.333333333333332</v>
       </c>
       <c r="K22" s="3" t="s">
@@ -4093,14 +4093,14 @@
       <c r="M22" s="1"/>
       <c r="N22" s="1"/>
     </row>
-    <row r="23" spans="1:14" ht="18" x14ac:dyDescent="0.4">
-      <c r="A23" s="9">
+    <row r="23" spans="1:14" ht="18" x14ac:dyDescent="0.35">
+      <c r="A23" s="8">
         <v>8</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="B23" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C23" s="9">
+      <c r="C23" s="8">
         <v>21</v>
       </c>
       <c r="E23" s="3">
@@ -4118,8 +4118,8 @@
       <c r="I23" s="3">
         <v>21</v>
       </c>
-      <c r="J23" s="11">
-        <f xml:space="preserve"> AVERAGE(G23:I23)</f>
+      <c r="J23" s="9">
+        <f t="shared" si="0"/>
         <v>21.333333333333332</v>
       </c>
       <c r="K23" s="3" t="s">
@@ -4131,14 +4131,14 @@
       <c r="M23" s="1"/>
       <c r="N23" s="1"/>
     </row>
-    <row r="24" spans="1:14" ht="18" x14ac:dyDescent="0.4">
-      <c r="A24" s="9">
+    <row r="24" spans="1:14" ht="18" x14ac:dyDescent="0.35">
+      <c r="A24" s="8">
         <v>11</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="B24" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="C24" s="9">
+      <c r="C24" s="8">
         <v>22</v>
       </c>
       <c r="E24" s="3">
@@ -4156,8 +4156,8 @@
       <c r="I24" s="3">
         <v>22</v>
       </c>
-      <c r="J24" s="11">
-        <f xml:space="preserve"> AVERAGE(G24:I24)</f>
+      <c r="J24" s="9">
+        <f t="shared" si="0"/>
         <v>20.333333333333332</v>
       </c>
       <c r="K24" s="3" t="s">
@@ -4169,14 +4169,14 @@
       <c r="M24" s="1"/>
       <c r="N24" s="1"/>
     </row>
-    <row r="25" spans="1:14" ht="18" x14ac:dyDescent="0.4">
-      <c r="A25" s="9">
+    <row r="25" spans="1:14" ht="18" x14ac:dyDescent="0.35">
+      <c r="A25" s="8">
         <v>15</v>
       </c>
-      <c r="B25" s="9" t="s">
+      <c r="B25" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C25" s="9">
+      <c r="C25" s="8">
         <v>23</v>
       </c>
       <c r="E25" s="3">
@@ -4194,8 +4194,8 @@
       <c r="I25" s="3">
         <v>23</v>
       </c>
-      <c r="J25" s="11">
-        <f xml:space="preserve"> AVERAGE(G25:I25)</f>
+      <c r="J25" s="9">
+        <f t="shared" si="0"/>
         <v>23</v>
       </c>
       <c r="K25" s="3" t="s">
@@ -4207,14 +4207,14 @@
       <c r="M25" s="1"/>
       <c r="N25" s="1"/>
     </row>
-    <row r="26" spans="1:14" ht="18" x14ac:dyDescent="0.4">
-      <c r="A26" s="9">
+    <row r="26" spans="1:14" ht="18" x14ac:dyDescent="0.35">
+      <c r="A26" s="8">
         <v>20</v>
       </c>
-      <c r="B26" s="9" t="s">
+      <c r="B26" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="C26" s="9">
+      <c r="C26" s="8">
         <v>24</v>
       </c>
       <c r="E26" s="3">
@@ -4232,8 +4232,8 @@
       <c r="I26" s="3">
         <v>24</v>
       </c>
-      <c r="J26" s="11">
-        <f xml:space="preserve"> AVERAGE(G26:I26)</f>
+      <c r="J26" s="9">
+        <f t="shared" si="0"/>
         <v>24.333333333333332</v>
       </c>
       <c r="K26" s="3" t="s">
@@ -4245,14 +4245,14 @@
       <c r="M26" s="1"/>
       <c r="N26" s="1"/>
     </row>
-    <row r="27" spans="1:14" ht="18" x14ac:dyDescent="0.4">
-      <c r="A27" s="9">
+    <row r="27" spans="1:14" ht="18" x14ac:dyDescent="0.35">
+      <c r="A27" s="8">
         <v>23</v>
       </c>
-      <c r="B27" s="9" t="s">
+      <c r="B27" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="C27" s="9">
+      <c r="C27" s="8">
         <v>25</v>
       </c>
       <c r="E27" s="3">
@@ -4270,8 +4270,8 @@
       <c r="I27" s="3">
         <v>25</v>
       </c>
-      <c r="J27" s="11">
-        <f xml:space="preserve"> AVERAGE(G27:I27)</f>
+      <c r="J27" s="9">
+        <f t="shared" si="0"/>
         <v>24.666666666666668</v>
       </c>
       <c r="K27" s="3" t="s">
@@ -4283,14 +4283,14 @@
       <c r="M27" s="1"/>
       <c r="N27" s="1"/>
     </row>
-    <row r="29" spans="1:14" ht="18" x14ac:dyDescent="0.4">
-      <c r="A29" s="5" t="s">
+    <row r="29" spans="1:14" ht="18" x14ac:dyDescent="0.35">
+      <c r="A29" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="B29" s="5"/>
-      <c r="C29" s="5"/>
-    </row>
-    <row r="30" spans="1:14" ht="18" x14ac:dyDescent="0.4">
+      <c r="B29" s="10"/>
+      <c r="C29" s="10"/>
+    </row>
+    <row r="30" spans="1:14" ht="18" x14ac:dyDescent="0.35">
       <c r="A30" s="3" t="s">
         <v>0</v>
       </c>
@@ -4301,7 +4301,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="18" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:14" ht="18" x14ac:dyDescent="0.35">
       <c r="A31" s="3">
         <v>5</v>
       </c>
@@ -4312,7 +4312,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="18" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:14" ht="18" x14ac:dyDescent="0.35">
       <c r="A32" s="3">
         <v>3</v>
       </c>
@@ -4323,7 +4323,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="18" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:3" ht="18" x14ac:dyDescent="0.35">
       <c r="A33" s="3">
         <v>2</v>
       </c>
@@ -4334,7 +4334,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="18" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:3" ht="18" x14ac:dyDescent="0.35">
       <c r="A34" s="3">
         <v>6</v>
       </c>
@@ -4345,7 +4345,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="18" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:3" ht="18" x14ac:dyDescent="0.35">
       <c r="A35" s="3">
         <v>17</v>
       </c>
@@ -4356,7 +4356,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="18" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:3" ht="18" x14ac:dyDescent="0.35">
       <c r="A36" s="3">
         <v>1</v>
       </c>
@@ -4367,7 +4367,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="18" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:3" ht="18" x14ac:dyDescent="0.35">
       <c r="A37" s="3">
         <v>12</v>
       </c>
@@ -4378,7 +4378,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="18" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:3" ht="18" x14ac:dyDescent="0.35">
       <c r="A38" s="3">
         <v>19</v>
       </c>
@@ -4389,7 +4389,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="18" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:3" ht="18" x14ac:dyDescent="0.35">
       <c r="A39" s="3">
         <v>7</v>
       </c>
@@ -4400,7 +4400,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="18" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:3" ht="18" x14ac:dyDescent="0.35">
       <c r="A40" s="3">
         <v>24</v>
       </c>
@@ -4411,7 +4411,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="18" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:3" ht="18" x14ac:dyDescent="0.35">
       <c r="A41" s="3">
         <v>4</v>
       </c>
@@ -4422,7 +4422,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="18" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:3" ht="18" x14ac:dyDescent="0.35">
       <c r="A42" s="3">
         <v>9</v>
       </c>
@@ -4433,7 +4433,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="18" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:3" ht="18" x14ac:dyDescent="0.35">
       <c r="A43" s="3">
         <v>10</v>
       </c>
@@ -4444,7 +4444,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="18" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:3" ht="18" x14ac:dyDescent="0.35">
       <c r="A44" s="3">
         <v>21</v>
       </c>
@@ -4455,7 +4455,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="18" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:3" ht="18" x14ac:dyDescent="0.35">
       <c r="A45" s="3">
         <v>18</v>
       </c>
@@ -4466,7 +4466,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="18" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:3" ht="18" x14ac:dyDescent="0.35">
       <c r="A46" s="3">
         <v>22</v>
       </c>
@@ -4477,7 +4477,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="18" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:3" ht="18" x14ac:dyDescent="0.35">
       <c r="A47" s="3">
         <v>11</v>
       </c>
@@ -4488,7 +4488,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="18" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:3" ht="18" x14ac:dyDescent="0.35">
       <c r="A48" s="3">
         <v>13</v>
       </c>
@@ -4499,7 +4499,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="18" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:3" ht="18" x14ac:dyDescent="0.35">
       <c r="A49" s="3">
         <v>14</v>
       </c>
@@ -4510,7 +4510,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="18" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:3" ht="18" x14ac:dyDescent="0.35">
       <c r="A50" s="3">
         <v>25</v>
       </c>
@@ -4521,7 +4521,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="18" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:3" ht="18" x14ac:dyDescent="0.35">
       <c r="A51" s="3">
         <v>16</v>
       </c>
@@ -4532,7 +4532,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="18" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:3" ht="18" x14ac:dyDescent="0.35">
       <c r="A52" s="3">
         <v>8</v>
       </c>
@@ -4543,7 +4543,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="18" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:3" ht="18" x14ac:dyDescent="0.35">
       <c r="A53" s="3">
         <v>15</v>
       </c>
@@ -4554,7 +4554,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="18" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:3" ht="18" x14ac:dyDescent="0.35">
       <c r="A54" s="3">
         <v>23</v>
       </c>
@@ -4565,7 +4565,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="18" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:3" ht="18" x14ac:dyDescent="0.35">
       <c r="A55" s="3">
         <v>20</v>
       </c>
@@ -4576,14 +4576,14 @@
         <v>25</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="18" x14ac:dyDescent="0.4">
-      <c r="A57" s="5" t="s">
+    <row r="57" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+      <c r="A57" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="B57" s="5"/>
-      <c r="C57" s="5"/>
-    </row>
-    <row r="58" spans="1:3" ht="18" x14ac:dyDescent="0.4">
+      <c r="B57" s="10"/>
+      <c r="C57" s="10"/>
+    </row>
+    <row r="58" spans="1:3" ht="18" x14ac:dyDescent="0.35">
       <c r="A58" s="3" t="s">
         <v>0</v>
       </c>
@@ -4594,7 +4594,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="18" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:3" ht="18" x14ac:dyDescent="0.35">
       <c r="A59" s="3">
         <v>2</v>
       </c>
@@ -4605,7 +4605,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="18" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:3" ht="18" x14ac:dyDescent="0.35">
       <c r="A60" s="3">
         <v>5</v>
       </c>
@@ -4616,7 +4616,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="18" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:3" ht="18" x14ac:dyDescent="0.35">
       <c r="A61" s="3">
         <v>6</v>
       </c>
@@ -4627,7 +4627,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="18" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:3" ht="18" x14ac:dyDescent="0.35">
       <c r="A62" s="3">
         <v>1</v>
       </c>
@@ -4638,7 +4638,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="18" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:3" ht="18" x14ac:dyDescent="0.35">
       <c r="A63" s="3">
         <v>19</v>
       </c>
@@ -4649,7 +4649,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="18" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:3" ht="18" x14ac:dyDescent="0.35">
       <c r="A64" s="3">
         <v>3</v>
       </c>
@@ -4660,7 +4660,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="18" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:3" ht="18" x14ac:dyDescent="0.35">
       <c r="A65" s="3">
         <v>12</v>
       </c>
@@ -4671,7 +4671,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="18" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:3" ht="18" x14ac:dyDescent="0.35">
       <c r="A66" s="3">
         <v>17</v>
       </c>
@@ -4682,7 +4682,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="18" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:3" ht="18" x14ac:dyDescent="0.35">
       <c r="A67" s="3">
         <v>4</v>
       </c>
@@ -4693,7 +4693,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="18" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:3" ht="18" x14ac:dyDescent="0.35">
       <c r="A68" s="3">
         <v>7</v>
       </c>
@@ -4704,7 +4704,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="18" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:3" ht="18" x14ac:dyDescent="0.35">
       <c r="A69" s="3">
         <v>24</v>
       </c>
@@ -4715,7 +4715,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="18" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:3" ht="18" x14ac:dyDescent="0.35">
       <c r="A70" s="3">
         <v>10</v>
       </c>
@@ -4726,7 +4726,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="71" spans="1:3" ht="18" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:3" ht="18" x14ac:dyDescent="0.35">
       <c r="A71" s="3">
         <v>18</v>
       </c>
@@ -4737,7 +4737,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="72" spans="1:3" ht="18" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:3" ht="18" x14ac:dyDescent="0.35">
       <c r="A72" s="3">
         <v>21</v>
       </c>
@@ -4748,7 +4748,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="73" spans="1:3" ht="18" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:3" ht="18" x14ac:dyDescent="0.35">
       <c r="A73" s="3">
         <v>13</v>
       </c>
@@ -4759,7 +4759,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="18" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:3" ht="18" x14ac:dyDescent="0.35">
       <c r="A74" s="3">
         <v>14</v>
       </c>
@@ -4770,7 +4770,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="75" spans="1:3" ht="18" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:3" ht="18" x14ac:dyDescent="0.35">
       <c r="A75" s="3">
         <v>22</v>
       </c>
@@ -4781,7 +4781,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="76" spans="1:3" ht="18" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:3" ht="18" x14ac:dyDescent="0.35">
       <c r="A76" s="3">
         <v>9</v>
       </c>
@@ -4792,7 +4792,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="18" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:3" ht="18" x14ac:dyDescent="0.35">
       <c r="A77" s="3">
         <v>25</v>
       </c>
@@ -4803,7 +4803,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="78" spans="1:3" ht="18" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:3" ht="18" x14ac:dyDescent="0.35">
       <c r="A78" s="3">
         <v>16</v>
       </c>
@@ -4814,7 +4814,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="79" spans="1:3" ht="18" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:3" ht="18" x14ac:dyDescent="0.35">
       <c r="A79" s="3">
         <v>8</v>
       </c>
@@ -4825,7 +4825,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="80" spans="1:3" ht="18" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:3" ht="18" x14ac:dyDescent="0.35">
       <c r="A80" s="3">
         <v>11</v>
       </c>
@@ -4836,7 +4836,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="81" spans="1:3" ht="18" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:3" ht="18" x14ac:dyDescent="0.35">
       <c r="A81" s="3">
         <v>15</v>
       </c>
@@ -4847,7 +4847,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="82" spans="1:3" ht="18" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:3" ht="18" x14ac:dyDescent="0.35">
       <c r="A82" s="3">
         <v>20</v>
       </c>
@@ -4858,7 +4858,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="18" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:3" ht="18" x14ac:dyDescent="0.35">
       <c r="A83" s="3">
         <v>23</v>
       </c>
@@ -4883,188 +4883,188 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A016DE5-AAB5-46C5-8125-ABC707C72B83}">
   <dimension ref="A1:AJ80"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="10" width="10.36328125" bestFit="1" customWidth="1"/>
-    <col min="11" max="26" width="11.6328125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="9.08984375" customWidth="1"/>
-    <col min="29" max="29" width="80.90625" bestFit="1" customWidth="1"/>
-    <col min="30" max="32" width="27.6328125" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="15.81640625" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="16.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="10" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="26" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="9.109375" customWidth="1"/>
+    <col min="29" max="29" width="80.88671875" bestFit="1" customWidth="1"/>
+    <col min="30" max="32" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="16.109375" bestFit="1" customWidth="1"/>
     <col min="35" max="35" width="22" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="5.90625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="5.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="18" x14ac:dyDescent="0.4">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:36" ht="18" x14ac:dyDescent="0.35">
+      <c r="A1" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="K1" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="L1" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="M1" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="N1" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="O1" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="P1" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="Q1" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="R1" s="6" t="s">
+      <c r="R1" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="S1" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="T1" s="6" t="s">
+      <c r="T1" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="U1" s="6" t="s">
+      <c r="U1" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="V1" s="6" t="s">
+      <c r="V1" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="W1" s="6" t="s">
+      <c r="W1" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="X1" s="6" t="s">
+      <c r="X1" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="Y1" s="6" t="s">
+      <c r="Y1" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="Z1" s="6" t="s">
+      <c r="Z1" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="AB1" s="5" t="s">
+      <c r="AB1" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="AC1" s="5"/>
-      <c r="AD1" s="5"/>
-      <c r="AE1" s="5"/>
-      <c r="AF1" s="5"/>
-      <c r="AG1" s="5"/>
-      <c r="AH1" s="5"/>
-      <c r="AI1" s="5"/>
-      <c r="AJ1" s="5"/>
-    </row>
-    <row r="2" spans="1:36" ht="18" x14ac:dyDescent="0.4">
-      <c r="A2" s="6" t="s">
+      <c r="AC1" s="10"/>
+      <c r="AD1" s="10"/>
+      <c r="AE1" s="10"/>
+      <c r="AF1" s="10"/>
+      <c r="AG1" s="10"/>
+      <c r="AH1" s="10"/>
+      <c r="AI1" s="10"/>
+      <c r="AJ1" s="10"/>
+    </row>
+    <row r="2" spans="1:36" ht="18" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="5">
         <v>1</v>
       </c>
-      <c r="C2" s="6">
-        <v>0</v>
-      </c>
-      <c r="D2" s="6">
-        <v>2</v>
-      </c>
-      <c r="E2" s="6">
-        <v>2</v>
-      </c>
-      <c r="F2" s="6">
-        <v>0</v>
-      </c>
-      <c r="G2" s="6">
-        <v>0</v>
-      </c>
-      <c r="H2" s="6">
-        <v>2</v>
-      </c>
-      <c r="I2" s="6">
-        <v>2</v>
-      </c>
-      <c r="J2" s="6">
-        <v>2</v>
-      </c>
-      <c r="K2" s="6">
-        <v>2</v>
-      </c>
-      <c r="L2" s="6">
-        <v>2</v>
-      </c>
-      <c r="M2" s="6">
-        <v>0</v>
-      </c>
-      <c r="N2" s="6">
-        <v>2</v>
-      </c>
-      <c r="O2" s="6">
-        <v>2</v>
-      </c>
-      <c r="P2" s="6">
-        <v>2</v>
-      </c>
-      <c r="Q2" s="6">
-        <v>2</v>
-      </c>
-      <c r="R2" s="6">
-        <v>0</v>
-      </c>
-      <c r="S2" s="6">
-        <v>2</v>
-      </c>
-      <c r="T2" s="6">
-        <v>0</v>
-      </c>
-      <c r="U2" s="6">
-        <v>2</v>
-      </c>
-      <c r="V2" s="6">
-        <v>2</v>
-      </c>
-      <c r="W2" s="6">
-        <v>2</v>
-      </c>
-      <c r="X2" s="6">
-        <v>2</v>
-      </c>
-      <c r="Y2" s="6">
-        <v>2</v>
-      </c>
-      <c r="Z2" s="6">
+      <c r="C2" s="5">
+        <v>0</v>
+      </c>
+      <c r="D2" s="5">
+        <v>2</v>
+      </c>
+      <c r="E2" s="5">
+        <v>2</v>
+      </c>
+      <c r="F2" s="5">
+        <v>0</v>
+      </c>
+      <c r="G2" s="5">
+        <v>0</v>
+      </c>
+      <c r="H2" s="5">
+        <v>2</v>
+      </c>
+      <c r="I2" s="5">
+        <v>2</v>
+      </c>
+      <c r="J2" s="5">
+        <v>2</v>
+      </c>
+      <c r="K2" s="5">
+        <v>2</v>
+      </c>
+      <c r="L2" s="5">
+        <v>2</v>
+      </c>
+      <c r="M2" s="5">
+        <v>0</v>
+      </c>
+      <c r="N2" s="5">
+        <v>2</v>
+      </c>
+      <c r="O2" s="5">
+        <v>2</v>
+      </c>
+      <c r="P2" s="5">
+        <v>2</v>
+      </c>
+      <c r="Q2" s="5">
+        <v>2</v>
+      </c>
+      <c r="R2" s="5">
+        <v>0</v>
+      </c>
+      <c r="S2" s="5">
+        <v>2</v>
+      </c>
+      <c r="T2" s="5">
+        <v>0</v>
+      </c>
+      <c r="U2" s="5">
+        <v>2</v>
+      </c>
+      <c r="V2" s="5">
+        <v>2</v>
+      </c>
+      <c r="W2" s="5">
+        <v>2</v>
+      </c>
+      <c r="X2" s="5">
+        <v>2</v>
+      </c>
+      <c r="Y2" s="5">
+        <v>2</v>
+      </c>
+      <c r="Z2" s="5">
         <v>2</v>
       </c>
       <c r="AB2" s="3" t="s">
@@ -5095,83 +5095,83 @@
         <v>72</v>
       </c>
     </row>
-    <row r="3" spans="1:36" ht="18" x14ac:dyDescent="0.4">
-      <c r="A3" s="6" t="s">
+    <row r="3" spans="1:36" ht="18" x14ac:dyDescent="0.35">
+      <c r="A3" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="B3" s="6">
-        <v>2</v>
-      </c>
-      <c r="C3" s="6">
+      <c r="B3" s="5">
+        <v>2</v>
+      </c>
+      <c r="C3" s="5">
         <v>1</v>
       </c>
-      <c r="D3" s="6">
-        <v>2</v>
-      </c>
-      <c r="E3" s="6">
-        <v>2</v>
-      </c>
-      <c r="F3" s="6">
-        <v>0</v>
-      </c>
-      <c r="G3" s="6">
-        <v>0</v>
-      </c>
-      <c r="H3" s="6">
-        <v>2</v>
-      </c>
-      <c r="I3" s="6">
-        <v>2</v>
-      </c>
-      <c r="J3" s="6">
-        <v>2</v>
-      </c>
-      <c r="K3" s="6">
-        <v>2</v>
-      </c>
-      <c r="L3" s="6">
-        <v>2</v>
-      </c>
-      <c r="M3" s="6">
-        <v>0</v>
-      </c>
-      <c r="N3" s="6">
-        <v>2</v>
-      </c>
-      <c r="O3" s="6">
-        <v>2</v>
-      </c>
-      <c r="P3" s="6">
-        <v>2</v>
-      </c>
-      <c r="Q3" s="6">
-        <v>2</v>
-      </c>
-      <c r="R3" s="6">
-        <v>0</v>
-      </c>
-      <c r="S3" s="6">
-        <v>2</v>
-      </c>
-      <c r="T3" s="6">
-        <v>0</v>
-      </c>
-      <c r="U3" s="6">
-        <v>2</v>
-      </c>
-      <c r="V3" s="6">
-        <v>2</v>
-      </c>
-      <c r="W3" s="6">
-        <v>2</v>
-      </c>
-      <c r="X3" s="6">
-        <v>2</v>
-      </c>
-      <c r="Y3" s="6">
-        <v>2</v>
-      </c>
-      <c r="Z3" s="6">
+      <c r="D3" s="5">
+        <v>2</v>
+      </c>
+      <c r="E3" s="5">
+        <v>2</v>
+      </c>
+      <c r="F3" s="5">
+        <v>0</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>2</v>
+      </c>
+      <c r="I3" s="5">
+        <v>2</v>
+      </c>
+      <c r="J3" s="5">
+        <v>2</v>
+      </c>
+      <c r="K3" s="5">
+        <v>2</v>
+      </c>
+      <c r="L3" s="5">
+        <v>2</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>2</v>
+      </c>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="5">
+        <v>2</v>
+      </c>
+      <c r="Q3" s="5">
+        <v>2</v>
+      </c>
+      <c r="R3" s="5">
+        <v>0</v>
+      </c>
+      <c r="S3" s="5">
+        <v>2</v>
+      </c>
+      <c r="T3" s="5">
+        <v>0</v>
+      </c>
+      <c r="U3" s="5">
+        <v>2</v>
+      </c>
+      <c r="V3" s="5">
+        <v>2</v>
+      </c>
+      <c r="W3" s="5">
+        <v>2</v>
+      </c>
+      <c r="X3" s="5">
+        <v>2</v>
+      </c>
+      <c r="Y3" s="5">
+        <v>2</v>
+      </c>
+      <c r="Z3" s="5">
         <v>2</v>
       </c>
       <c r="AB3" s="3">
@@ -5202,83 +5202,83 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:36" ht="18" x14ac:dyDescent="0.4">
-      <c r="A4" s="6" t="s">
+    <row r="4" spans="1:36" ht="18" x14ac:dyDescent="0.35">
+      <c r="A4" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="B4" s="6">
-        <v>0</v>
-      </c>
-      <c r="C4" s="6">
-        <v>0</v>
-      </c>
-      <c r="D4" s="6">
+      <c r="B4" s="5">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5">
         <v>1</v>
       </c>
-      <c r="E4" s="6">
-        <v>0</v>
-      </c>
-      <c r="F4" s="6">
-        <v>0</v>
-      </c>
-      <c r="G4" s="6">
-        <v>0</v>
-      </c>
-      <c r="H4" s="6">
-        <v>2</v>
-      </c>
-      <c r="I4" s="6">
-        <v>2</v>
-      </c>
-      <c r="J4" s="6">
-        <v>2</v>
-      </c>
-      <c r="K4" s="6">
-        <v>2</v>
-      </c>
-      <c r="L4" s="6">
-        <v>2</v>
-      </c>
-      <c r="M4" s="6">
-        <v>0</v>
-      </c>
-      <c r="N4" s="6">
-        <v>2</v>
-      </c>
-      <c r="O4" s="6">
-        <v>2</v>
-      </c>
-      <c r="P4" s="6">
-        <v>2</v>
-      </c>
-      <c r="Q4" s="6">
-        <v>2</v>
-      </c>
-      <c r="R4" s="6">
-        <v>0</v>
-      </c>
-      <c r="S4" s="6">
-        <v>2</v>
-      </c>
-      <c r="T4" s="6">
-        <v>0</v>
-      </c>
-      <c r="U4" s="6">
-        <v>2</v>
-      </c>
-      <c r="V4" s="6">
-        <v>2</v>
-      </c>
-      <c r="W4" s="6">
-        <v>2</v>
-      </c>
-      <c r="X4" s="6">
-        <v>2</v>
-      </c>
-      <c r="Y4" s="6">
-        <v>2</v>
-      </c>
-      <c r="Z4" s="6">
+      <c r="E4" s="5">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5">
+        <v>0</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5">
+        <v>2</v>
+      </c>
+      <c r="I4" s="5">
+        <v>2</v>
+      </c>
+      <c r="J4" s="5">
+        <v>2</v>
+      </c>
+      <c r="K4" s="5">
+        <v>2</v>
+      </c>
+      <c r="L4" s="5">
+        <v>2</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>2</v>
+      </c>
+      <c r="O4" s="5">
+        <v>2</v>
+      </c>
+      <c r="P4" s="5">
+        <v>2</v>
+      </c>
+      <c r="Q4" s="5">
+        <v>2</v>
+      </c>
+      <c r="R4" s="5">
+        <v>0</v>
+      </c>
+      <c r="S4" s="5">
+        <v>2</v>
+      </c>
+      <c r="T4" s="5">
+        <v>0</v>
+      </c>
+      <c r="U4" s="5">
+        <v>2</v>
+      </c>
+      <c r="V4" s="5">
+        <v>2</v>
+      </c>
+      <c r="W4" s="5">
+        <v>2</v>
+      </c>
+      <c r="X4" s="5">
+        <v>2</v>
+      </c>
+      <c r="Y4" s="5">
+        <v>2</v>
+      </c>
+      <c r="Z4" s="5">
         <v>2</v>
       </c>
       <c r="AB4" s="3">
@@ -5309,83 +5309,83 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:36" ht="18" x14ac:dyDescent="0.4">
-      <c r="A5" s="6" t="s">
+    <row r="5" spans="1:36" ht="18" x14ac:dyDescent="0.35">
+      <c r="A5" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="B5" s="6">
-        <v>0</v>
-      </c>
-      <c r="C5" s="6">
-        <v>0</v>
-      </c>
-      <c r="D5" s="6">
-        <v>2</v>
-      </c>
-      <c r="E5" s="6">
+      <c r="B5" s="5">
+        <v>0</v>
+      </c>
+      <c r="C5" s="5">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5">
+        <v>2</v>
+      </c>
+      <c r="E5" s="5">
         <v>1</v>
       </c>
-      <c r="F5" s="6">
-        <v>0</v>
-      </c>
-      <c r="G5" s="6">
-        <v>0</v>
-      </c>
-      <c r="H5" s="6">
-        <v>2</v>
-      </c>
-      <c r="I5" s="6">
-        <v>2</v>
-      </c>
-      <c r="J5" s="6">
-        <v>2</v>
-      </c>
-      <c r="K5" s="6">
-        <v>2</v>
-      </c>
-      <c r="L5" s="6">
-        <v>2</v>
-      </c>
-      <c r="M5" s="6">
-        <v>0</v>
-      </c>
-      <c r="N5" s="6">
-        <v>2</v>
-      </c>
-      <c r="O5" s="6">
-        <v>2</v>
-      </c>
-      <c r="P5" s="6">
-        <v>2</v>
-      </c>
-      <c r="Q5" s="6">
-        <v>2</v>
-      </c>
-      <c r="R5" s="6">
-        <v>0</v>
-      </c>
-      <c r="S5" s="6">
-        <v>2</v>
-      </c>
-      <c r="T5" s="6">
-        <v>0</v>
-      </c>
-      <c r="U5" s="6">
-        <v>2</v>
-      </c>
-      <c r="V5" s="6">
-        <v>2</v>
-      </c>
-      <c r="W5" s="6">
-        <v>2</v>
-      </c>
-      <c r="X5" s="6">
-        <v>2</v>
-      </c>
-      <c r="Y5" s="6">
-        <v>2</v>
-      </c>
-      <c r="Z5" s="6">
+      <c r="F5" s="5">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>2</v>
+      </c>
+      <c r="I5" s="5">
+        <v>2</v>
+      </c>
+      <c r="J5" s="5">
+        <v>2</v>
+      </c>
+      <c r="K5" s="5">
+        <v>2</v>
+      </c>
+      <c r="L5" s="5">
+        <v>2</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>2</v>
+      </c>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="5">
+        <v>2</v>
+      </c>
+      <c r="Q5" s="5">
+        <v>2</v>
+      </c>
+      <c r="R5" s="5">
+        <v>0</v>
+      </c>
+      <c r="S5" s="5">
+        <v>2</v>
+      </c>
+      <c r="T5" s="5">
+        <v>0</v>
+      </c>
+      <c r="U5" s="5">
+        <v>2</v>
+      </c>
+      <c r="V5" s="5">
+        <v>2</v>
+      </c>
+      <c r="W5" s="5">
+        <v>2</v>
+      </c>
+      <c r="X5" s="5">
+        <v>2</v>
+      </c>
+      <c r="Y5" s="5">
+        <v>2</v>
+      </c>
+      <c r="Z5" s="5">
         <v>2</v>
       </c>
       <c r="AB5" s="3">
@@ -5416,83 +5416,83 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:36" ht="18" x14ac:dyDescent="0.4">
-      <c r="A6" s="6" t="s">
+    <row r="6" spans="1:36" ht="18" x14ac:dyDescent="0.35">
+      <c r="A6" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="B6" s="6">
-        <v>2</v>
-      </c>
-      <c r="C6" s="6">
-        <v>2</v>
-      </c>
-      <c r="D6" s="6">
-        <v>2</v>
-      </c>
-      <c r="E6" s="6">
-        <v>2</v>
-      </c>
-      <c r="F6" s="6">
+      <c r="B6" s="5">
+        <v>2</v>
+      </c>
+      <c r="C6" s="5">
+        <v>2</v>
+      </c>
+      <c r="D6" s="5">
+        <v>2</v>
+      </c>
+      <c r="E6" s="5">
+        <v>2</v>
+      </c>
+      <c r="F6" s="5">
         <v>1</v>
       </c>
-      <c r="G6" s="6">
-        <v>2</v>
-      </c>
-      <c r="H6" s="6">
-        <v>2</v>
-      </c>
-      <c r="I6" s="6">
-        <v>2</v>
-      </c>
-      <c r="J6" s="6">
-        <v>2</v>
-      </c>
-      <c r="K6" s="6">
-        <v>2</v>
-      </c>
-      <c r="L6" s="6">
-        <v>2</v>
-      </c>
-      <c r="M6" s="6">
-        <v>2</v>
-      </c>
-      <c r="N6" s="6">
-        <v>2</v>
-      </c>
-      <c r="O6" s="6">
-        <v>2</v>
-      </c>
-      <c r="P6" s="6">
-        <v>2</v>
-      </c>
-      <c r="Q6" s="6">
-        <v>2</v>
-      </c>
-      <c r="R6" s="6">
-        <v>2</v>
-      </c>
-      <c r="S6" s="6">
-        <v>2</v>
-      </c>
-      <c r="T6" s="6">
-        <v>2</v>
-      </c>
-      <c r="U6" s="6">
-        <v>2</v>
-      </c>
-      <c r="V6" s="6">
-        <v>2</v>
-      </c>
-      <c r="W6" s="6">
-        <v>2</v>
-      </c>
-      <c r="X6" s="6">
-        <v>2</v>
-      </c>
-      <c r="Y6" s="6">
-        <v>2</v>
-      </c>
-      <c r="Z6" s="6">
+      <c r="G6" s="5">
+        <v>2</v>
+      </c>
+      <c r="H6" s="5">
+        <v>2</v>
+      </c>
+      <c r="I6" s="5">
+        <v>2</v>
+      </c>
+      <c r="J6" s="5">
+        <v>2</v>
+      </c>
+      <c r="K6" s="5">
+        <v>2</v>
+      </c>
+      <c r="L6" s="5">
+        <v>2</v>
+      </c>
+      <c r="M6" s="5">
+        <v>2</v>
+      </c>
+      <c r="N6" s="5">
+        <v>2</v>
+      </c>
+      <c r="O6" s="5">
+        <v>2</v>
+      </c>
+      <c r="P6" s="5">
+        <v>2</v>
+      </c>
+      <c r="Q6" s="5">
+        <v>2</v>
+      </c>
+      <c r="R6" s="5">
+        <v>2</v>
+      </c>
+      <c r="S6" s="5">
+        <v>2</v>
+      </c>
+      <c r="T6" s="5">
+        <v>2</v>
+      </c>
+      <c r="U6" s="5">
+        <v>2</v>
+      </c>
+      <c r="V6" s="5">
+        <v>2</v>
+      </c>
+      <c r="W6" s="5">
+        <v>2</v>
+      </c>
+      <c r="X6" s="5">
+        <v>2</v>
+      </c>
+      <c r="Y6" s="5">
+        <v>2</v>
+      </c>
+      <c r="Z6" s="5">
         <v>2</v>
       </c>
       <c r="AB6" s="3">
@@ -5523,83 +5523,83 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:36" ht="18" x14ac:dyDescent="0.4">
-      <c r="A7" s="6" t="s">
+    <row r="7" spans="1:36" ht="18" x14ac:dyDescent="0.35">
+      <c r="A7" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="B7" s="6">
-        <v>2</v>
-      </c>
-      <c r="C7" s="6">
-        <v>2</v>
-      </c>
-      <c r="D7" s="6">
-        <v>2</v>
-      </c>
-      <c r="E7" s="6">
-        <v>2</v>
-      </c>
-      <c r="F7" s="6">
-        <v>0</v>
-      </c>
-      <c r="G7" s="6">
+      <c r="B7" s="5">
+        <v>2</v>
+      </c>
+      <c r="C7" s="5">
+        <v>2</v>
+      </c>
+      <c r="D7" s="5">
+        <v>2</v>
+      </c>
+      <c r="E7" s="5">
+        <v>2</v>
+      </c>
+      <c r="F7" s="5">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5">
         <v>1</v>
       </c>
-      <c r="H7" s="6">
-        <v>2</v>
-      </c>
-      <c r="I7" s="6">
-        <v>2</v>
-      </c>
-      <c r="J7" s="6">
-        <v>2</v>
-      </c>
-      <c r="K7" s="6">
-        <v>2</v>
-      </c>
-      <c r="L7" s="6">
-        <v>2</v>
-      </c>
-      <c r="M7" s="6">
-        <v>2</v>
-      </c>
-      <c r="N7" s="6">
-        <v>2</v>
-      </c>
-      <c r="O7" s="6">
-        <v>2</v>
-      </c>
-      <c r="P7" s="6">
-        <v>2</v>
-      </c>
-      <c r="Q7" s="6">
-        <v>2</v>
-      </c>
-      <c r="R7" s="6">
-        <v>2</v>
-      </c>
-      <c r="S7" s="6">
-        <v>2</v>
-      </c>
-      <c r="T7" s="6">
-        <v>2</v>
-      </c>
-      <c r="U7" s="6">
-        <v>2</v>
-      </c>
-      <c r="V7" s="6">
-        <v>2</v>
-      </c>
-      <c r="W7" s="6">
-        <v>2</v>
-      </c>
-      <c r="X7" s="6">
-        <v>2</v>
-      </c>
-      <c r="Y7" s="6">
-        <v>2</v>
-      </c>
-      <c r="Z7" s="6">
+      <c r="H7" s="5">
+        <v>2</v>
+      </c>
+      <c r="I7" s="5">
+        <v>2</v>
+      </c>
+      <c r="J7" s="5">
+        <v>2</v>
+      </c>
+      <c r="K7" s="5">
+        <v>2</v>
+      </c>
+      <c r="L7" s="5">
+        <v>2</v>
+      </c>
+      <c r="M7" s="5">
+        <v>2</v>
+      </c>
+      <c r="N7" s="5">
+        <v>2</v>
+      </c>
+      <c r="O7" s="5">
+        <v>2</v>
+      </c>
+      <c r="P7" s="5">
+        <v>2</v>
+      </c>
+      <c r="Q7" s="5">
+        <v>2</v>
+      </c>
+      <c r="R7" s="5">
+        <v>2</v>
+      </c>
+      <c r="S7" s="5">
+        <v>2</v>
+      </c>
+      <c r="T7" s="5">
+        <v>2</v>
+      </c>
+      <c r="U7" s="5">
+        <v>2</v>
+      </c>
+      <c r="V7" s="5">
+        <v>2</v>
+      </c>
+      <c r="W7" s="5">
+        <v>2</v>
+      </c>
+      <c r="X7" s="5">
+        <v>2</v>
+      </c>
+      <c r="Y7" s="5">
+        <v>2</v>
+      </c>
+      <c r="Z7" s="5">
         <v>2</v>
       </c>
       <c r="AB7" s="3">
@@ -5630,83 +5630,83 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:36" ht="18" x14ac:dyDescent="0.4">
-      <c r="A8" s="6" t="s">
+    <row r="8" spans="1:36" ht="18" x14ac:dyDescent="0.35">
+      <c r="A8" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="B8" s="6">
-        <v>0</v>
-      </c>
-      <c r="C8" s="6">
-        <v>0</v>
-      </c>
-      <c r="D8" s="6">
-        <v>0</v>
-      </c>
-      <c r="E8" s="6">
-        <v>0</v>
-      </c>
-      <c r="F8" s="6">
-        <v>0</v>
-      </c>
-      <c r="G8" s="6">
-        <v>0</v>
-      </c>
-      <c r="H8" s="6">
+      <c r="B8" s="5">
+        <v>0</v>
+      </c>
+      <c r="C8" s="5">
+        <v>0</v>
+      </c>
+      <c r="D8" s="5">
+        <v>0</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5">
+        <v>0</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
         <v>1</v>
       </c>
-      <c r="I8" s="6">
-        <v>2</v>
-      </c>
-      <c r="J8" s="6">
-        <v>2</v>
-      </c>
-      <c r="K8" s="6">
-        <v>2</v>
-      </c>
-      <c r="L8" s="6">
-        <v>2</v>
-      </c>
-      <c r="M8" s="6">
-        <v>0</v>
-      </c>
-      <c r="N8" s="6">
-        <v>2</v>
-      </c>
-      <c r="O8" s="6">
-        <v>2</v>
-      </c>
-      <c r="P8" s="6">
-        <v>2</v>
-      </c>
-      <c r="Q8" s="6">
-        <v>2</v>
-      </c>
-      <c r="R8" s="6">
-        <v>0</v>
-      </c>
-      <c r="S8" s="6">
-        <v>2</v>
-      </c>
-      <c r="T8" s="6">
-        <v>0</v>
-      </c>
-      <c r="U8" s="6">
-        <v>2</v>
-      </c>
-      <c r="V8" s="6">
-        <v>2</v>
-      </c>
-      <c r="W8" s="6">
-        <v>2</v>
-      </c>
-      <c r="X8" s="6">
-        <v>2</v>
-      </c>
-      <c r="Y8" s="6">
-        <v>2</v>
-      </c>
-      <c r="Z8" s="6">
+      <c r="I8" s="5">
+        <v>2</v>
+      </c>
+      <c r="J8" s="5">
+        <v>2</v>
+      </c>
+      <c r="K8" s="5">
+        <v>2</v>
+      </c>
+      <c r="L8" s="5">
+        <v>2</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>2</v>
+      </c>
+      <c r="O8" s="5">
+        <v>2</v>
+      </c>
+      <c r="P8" s="5">
+        <v>2</v>
+      </c>
+      <c r="Q8" s="5">
+        <v>2</v>
+      </c>
+      <c r="R8" s="5">
+        <v>0</v>
+      </c>
+      <c r="S8" s="5">
+        <v>2</v>
+      </c>
+      <c r="T8" s="5">
+        <v>0</v>
+      </c>
+      <c r="U8" s="5">
+        <v>2</v>
+      </c>
+      <c r="V8" s="5">
+        <v>2</v>
+      </c>
+      <c r="W8" s="5">
+        <v>2</v>
+      </c>
+      <c r="X8" s="5">
+        <v>2</v>
+      </c>
+      <c r="Y8" s="5">
+        <v>2</v>
+      </c>
+      <c r="Z8" s="5">
         <v>2</v>
       </c>
       <c r="AB8" s="3">
@@ -5737,83 +5737,83 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:36" ht="18" x14ac:dyDescent="0.4">
-      <c r="A9" s="6" t="s">
+    <row r="9" spans="1:36" ht="18" x14ac:dyDescent="0.35">
+      <c r="A9" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="B9" s="6">
-        <v>0</v>
-      </c>
-      <c r="C9" s="6">
-        <v>0</v>
-      </c>
-      <c r="D9" s="6">
-        <v>0</v>
-      </c>
-      <c r="E9" s="6">
-        <v>0</v>
-      </c>
-      <c r="F9" s="6">
-        <v>0</v>
-      </c>
-      <c r="G9" s="6">
-        <v>0</v>
-      </c>
-      <c r="H9" s="6">
-        <v>0</v>
-      </c>
-      <c r="I9" s="6">
+      <c r="B9" s="5">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5">
+        <v>0</v>
+      </c>
+      <c r="D9" s="5">
+        <v>0</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0</v>
+      </c>
+      <c r="F9" s="5">
+        <v>0</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
+        <v>0</v>
+      </c>
+      <c r="I9" s="5">
         <v>1</v>
       </c>
-      <c r="J9" s="6">
-        <v>2</v>
-      </c>
-      <c r="K9" s="6">
-        <v>0</v>
-      </c>
-      <c r="L9" s="6">
-        <v>2</v>
-      </c>
-      <c r="M9" s="6">
-        <v>0</v>
-      </c>
-      <c r="N9" s="6">
-        <v>2</v>
-      </c>
-      <c r="O9" s="6">
-        <v>2</v>
-      </c>
-      <c r="P9" s="6">
-        <v>2</v>
-      </c>
-      <c r="Q9" s="6">
-        <v>2</v>
-      </c>
-      <c r="R9" s="6">
-        <v>0</v>
-      </c>
-      <c r="S9" s="6">
-        <v>2</v>
-      </c>
-      <c r="T9" s="6">
-        <v>0</v>
-      </c>
-      <c r="U9" s="6">
-        <v>2</v>
-      </c>
-      <c r="V9" s="6">
-        <v>2</v>
-      </c>
-      <c r="W9" s="6">
-        <v>2</v>
-      </c>
-      <c r="X9" s="6">
-        <v>2</v>
-      </c>
-      <c r="Y9" s="6">
-        <v>2</v>
-      </c>
-      <c r="Z9" s="6">
+      <c r="J9" s="5">
+        <v>2</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>2</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>2</v>
+      </c>
+      <c r="O9" s="5">
+        <v>2</v>
+      </c>
+      <c r="P9" s="5">
+        <v>2</v>
+      </c>
+      <c r="Q9" s="5">
+        <v>2</v>
+      </c>
+      <c r="R9" s="5">
+        <v>0</v>
+      </c>
+      <c r="S9" s="5">
+        <v>2</v>
+      </c>
+      <c r="T9" s="5">
+        <v>0</v>
+      </c>
+      <c r="U9" s="5">
+        <v>2</v>
+      </c>
+      <c r="V9" s="5">
+        <v>2</v>
+      </c>
+      <c r="W9" s="5">
+        <v>2</v>
+      </c>
+      <c r="X9" s="5">
+        <v>2</v>
+      </c>
+      <c r="Y9" s="5">
+        <v>2</v>
+      </c>
+      <c r="Z9" s="5">
         <v>2</v>
       </c>
       <c r="AB9" s="3">
@@ -5844,83 +5844,83 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:36" ht="18" x14ac:dyDescent="0.4">
-      <c r="A10" s="6" t="s">
+    <row r="10" spans="1:36" ht="18" x14ac:dyDescent="0.35">
+      <c r="A10" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="B10" s="6">
-        <v>0</v>
-      </c>
-      <c r="C10" s="6">
-        <v>0</v>
-      </c>
-      <c r="D10" s="6">
-        <v>0</v>
-      </c>
-      <c r="E10" s="6">
-        <v>0</v>
-      </c>
-      <c r="F10" s="6">
-        <v>0</v>
-      </c>
-      <c r="G10" s="6">
-        <v>0</v>
-      </c>
-      <c r="H10" s="6">
-        <v>0</v>
-      </c>
-      <c r="I10" s="6">
-        <v>0</v>
-      </c>
-      <c r="J10" s="6">
+      <c r="B10" s="5">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5">
+        <v>0</v>
+      </c>
+      <c r="D10" s="5">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5">
+        <v>0</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5">
         <v>1</v>
       </c>
-      <c r="K10" s="6">
-        <v>0</v>
-      </c>
-      <c r="L10" s="6">
-        <v>2</v>
-      </c>
-      <c r="M10" s="6">
-        <v>0</v>
-      </c>
-      <c r="N10" s="6">
-        <v>2</v>
-      </c>
-      <c r="O10" s="6">
-        <v>2</v>
-      </c>
-      <c r="P10" s="6">
-        <v>2</v>
-      </c>
-      <c r="Q10" s="6">
-        <v>2</v>
-      </c>
-      <c r="R10" s="6">
-        <v>0</v>
-      </c>
-      <c r="S10" s="6">
-        <v>2</v>
-      </c>
-      <c r="T10" s="6">
-        <v>0</v>
-      </c>
-      <c r="U10" s="6">
-        <v>2</v>
-      </c>
-      <c r="V10" s="6">
-        <v>2</v>
-      </c>
-      <c r="W10" s="6">
-        <v>2</v>
-      </c>
-      <c r="X10" s="6">
-        <v>2</v>
-      </c>
-      <c r="Y10" s="6">
-        <v>2</v>
-      </c>
-      <c r="Z10" s="6">
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>2</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>2</v>
+      </c>
+      <c r="O10" s="5">
+        <v>2</v>
+      </c>
+      <c r="P10" s="5">
+        <v>2</v>
+      </c>
+      <c r="Q10" s="5">
+        <v>2</v>
+      </c>
+      <c r="R10" s="5">
+        <v>0</v>
+      </c>
+      <c r="S10" s="5">
+        <v>2</v>
+      </c>
+      <c r="T10" s="5">
+        <v>0</v>
+      </c>
+      <c r="U10" s="5">
+        <v>2</v>
+      </c>
+      <c r="V10" s="5">
+        <v>2</v>
+      </c>
+      <c r="W10" s="5">
+        <v>2</v>
+      </c>
+      <c r="X10" s="5">
+        <v>2</v>
+      </c>
+      <c r="Y10" s="5">
+        <v>2</v>
+      </c>
+      <c r="Z10" s="5">
         <v>2</v>
       </c>
       <c r="AB10" s="3">
@@ -5951,83 +5951,83 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:36" ht="18" x14ac:dyDescent="0.4">
-      <c r="A11" s="6" t="s">
+    <row r="11" spans="1:36" ht="18" x14ac:dyDescent="0.35">
+      <c r="A11" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="B11" s="6">
-        <v>0</v>
-      </c>
-      <c r="C11" s="6">
-        <v>0</v>
-      </c>
-      <c r="D11" s="6">
-        <v>0</v>
-      </c>
-      <c r="E11" s="6">
-        <v>0</v>
-      </c>
-      <c r="F11" s="6">
-        <v>0</v>
-      </c>
-      <c r="G11" s="6">
-        <v>0</v>
-      </c>
-      <c r="H11" s="6">
-        <v>0</v>
-      </c>
-      <c r="I11" s="6">
-        <v>2</v>
-      </c>
-      <c r="J11" s="6">
-        <v>2</v>
-      </c>
-      <c r="K11" s="6">
+      <c r="B11" s="5">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5">
+        <v>0</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5">
+        <v>0</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5">
+        <v>2</v>
+      </c>
+      <c r="J11" s="5">
+        <v>2</v>
+      </c>
+      <c r="K11" s="5">
         <v>1</v>
       </c>
-      <c r="L11" s="6">
-        <v>2</v>
-      </c>
-      <c r="M11" s="6">
-        <v>0</v>
-      </c>
-      <c r="N11" s="6">
-        <v>2</v>
-      </c>
-      <c r="O11" s="6">
-        <v>2</v>
-      </c>
-      <c r="P11" s="6">
-        <v>2</v>
-      </c>
-      <c r="Q11" s="6">
-        <v>2</v>
-      </c>
-      <c r="R11" s="6">
-        <v>0</v>
-      </c>
-      <c r="S11" s="6">
-        <v>2</v>
-      </c>
-      <c r="T11" s="6">
-        <v>0</v>
-      </c>
-      <c r="U11" s="6">
-        <v>2</v>
-      </c>
-      <c r="V11" s="6">
-        <v>2</v>
-      </c>
-      <c r="W11" s="6">
-        <v>2</v>
-      </c>
-      <c r="X11" s="6">
-        <v>2</v>
-      </c>
-      <c r="Y11" s="6">
-        <v>2</v>
-      </c>
-      <c r="Z11" s="6">
+      <c r="L11" s="5">
+        <v>2</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>2</v>
+      </c>
+      <c r="O11" s="5">
+        <v>2</v>
+      </c>
+      <c r="P11" s="5">
+        <v>2</v>
+      </c>
+      <c r="Q11" s="5">
+        <v>2</v>
+      </c>
+      <c r="R11" s="5">
+        <v>0</v>
+      </c>
+      <c r="S11" s="5">
+        <v>2</v>
+      </c>
+      <c r="T11" s="5">
+        <v>0</v>
+      </c>
+      <c r="U11" s="5">
+        <v>2</v>
+      </c>
+      <c r="V11" s="5">
+        <v>2</v>
+      </c>
+      <c r="W11" s="5">
+        <v>2</v>
+      </c>
+      <c r="X11" s="5">
+        <v>2</v>
+      </c>
+      <c r="Y11" s="5">
+        <v>2</v>
+      </c>
+      <c r="Z11" s="5">
         <v>2</v>
       </c>
       <c r="AB11" s="3">
@@ -6058,83 +6058,83 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:36" ht="18" x14ac:dyDescent="0.4">
-      <c r="A12" s="6" t="s">
+    <row r="12" spans="1:36" ht="18" x14ac:dyDescent="0.35">
+      <c r="A12" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="B12" s="6">
-        <v>0</v>
-      </c>
-      <c r="C12" s="6">
-        <v>0</v>
-      </c>
-      <c r="D12" s="6">
-        <v>0</v>
-      </c>
-      <c r="E12" s="6">
-        <v>0</v>
-      </c>
-      <c r="F12" s="6">
-        <v>0</v>
-      </c>
-      <c r="G12" s="6">
-        <v>0</v>
-      </c>
-      <c r="H12" s="6">
-        <v>0</v>
-      </c>
-      <c r="I12" s="6">
-        <v>0</v>
-      </c>
-      <c r="J12" s="6">
-        <v>0</v>
-      </c>
-      <c r="K12" s="6">
-        <v>0</v>
-      </c>
-      <c r="L12" s="6">
+      <c r="B12" s="5">
+        <v>0</v>
+      </c>
+      <c r="C12" s="5">
+        <v>0</v>
+      </c>
+      <c r="D12" s="5">
+        <v>0</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5">
+        <v>0</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5">
+        <v>0</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
         <v>1</v>
       </c>
-      <c r="M12" s="6">
-        <v>0</v>
-      </c>
-      <c r="N12" s="6">
-        <v>2</v>
-      </c>
-      <c r="O12" s="6">
-        <v>2</v>
-      </c>
-      <c r="P12" s="6">
-        <v>2</v>
-      </c>
-      <c r="Q12" s="6">
-        <v>2</v>
-      </c>
-      <c r="R12" s="6">
-        <v>0</v>
-      </c>
-      <c r="S12" s="6">
-        <v>2</v>
-      </c>
-      <c r="T12" s="6">
-        <v>0</v>
-      </c>
-      <c r="U12" s="6">
-        <v>2</v>
-      </c>
-      <c r="V12" s="6">
-        <v>2</v>
-      </c>
-      <c r="W12" s="6">
-        <v>2</v>
-      </c>
-      <c r="X12" s="6">
-        <v>2</v>
-      </c>
-      <c r="Y12" s="6">
-        <v>2</v>
-      </c>
-      <c r="Z12" s="6">
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>2</v>
+      </c>
+      <c r="O12" s="5">
+        <v>2</v>
+      </c>
+      <c r="P12" s="5">
+        <v>2</v>
+      </c>
+      <c r="Q12" s="5">
+        <v>2</v>
+      </c>
+      <c r="R12" s="5">
+        <v>0</v>
+      </c>
+      <c r="S12" s="5">
+        <v>2</v>
+      </c>
+      <c r="T12" s="5">
+        <v>0</v>
+      </c>
+      <c r="U12" s="5">
+        <v>2</v>
+      </c>
+      <c r="V12" s="5">
+        <v>2</v>
+      </c>
+      <c r="W12" s="5">
+        <v>2</v>
+      </c>
+      <c r="X12" s="5">
+        <v>2</v>
+      </c>
+      <c r="Y12" s="5">
+        <v>2</v>
+      </c>
+      <c r="Z12" s="5">
         <v>2</v>
       </c>
       <c r="AB12" s="3">
@@ -6165,83 +6165,83 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:36" ht="18" x14ac:dyDescent="0.4">
-      <c r="A13" s="6" t="s">
+    <row r="13" spans="1:36" ht="18" x14ac:dyDescent="0.35">
+      <c r="A13" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="B13" s="6">
-        <v>2</v>
-      </c>
-      <c r="C13" s="6">
-        <v>2</v>
-      </c>
-      <c r="D13" s="6">
-        <v>2</v>
-      </c>
-      <c r="E13" s="6">
-        <v>2</v>
-      </c>
-      <c r="F13" s="6">
-        <v>0</v>
-      </c>
-      <c r="G13" s="6">
-        <v>0</v>
-      </c>
-      <c r="H13" s="6">
-        <v>2</v>
-      </c>
-      <c r="I13" s="6">
-        <v>2</v>
-      </c>
-      <c r="J13" s="6">
-        <v>2</v>
-      </c>
-      <c r="K13" s="6">
-        <v>2</v>
-      </c>
-      <c r="L13" s="6">
-        <v>2</v>
-      </c>
-      <c r="M13" s="6">
+      <c r="B13" s="5">
+        <v>2</v>
+      </c>
+      <c r="C13" s="5">
+        <v>2</v>
+      </c>
+      <c r="D13" s="5">
+        <v>2</v>
+      </c>
+      <c r="E13" s="5">
+        <v>2</v>
+      </c>
+      <c r="F13" s="5">
+        <v>0</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5">
+        <v>2</v>
+      </c>
+      <c r="I13" s="5">
+        <v>2</v>
+      </c>
+      <c r="J13" s="5">
+        <v>2</v>
+      </c>
+      <c r="K13" s="5">
+        <v>2</v>
+      </c>
+      <c r="L13" s="5">
+        <v>2</v>
+      </c>
+      <c r="M13" s="5">
         <v>1</v>
       </c>
-      <c r="N13" s="6">
-        <v>2</v>
-      </c>
-      <c r="O13" s="6">
-        <v>2</v>
-      </c>
-      <c r="P13" s="6">
-        <v>2</v>
-      </c>
-      <c r="Q13" s="6">
-        <v>2</v>
-      </c>
-      <c r="R13" s="6">
-        <v>2</v>
-      </c>
-      <c r="S13" s="6">
-        <v>2</v>
-      </c>
-      <c r="T13" s="6">
-        <v>2</v>
-      </c>
-      <c r="U13" s="6">
-        <v>2</v>
-      </c>
-      <c r="V13" s="6">
-        <v>2</v>
-      </c>
-      <c r="W13" s="6">
-        <v>2</v>
-      </c>
-      <c r="X13" s="6">
-        <v>2</v>
-      </c>
-      <c r="Y13" s="6">
-        <v>2</v>
-      </c>
-      <c r="Z13" s="6">
+      <c r="N13" s="5">
+        <v>2</v>
+      </c>
+      <c r="O13" s="5">
+        <v>2</v>
+      </c>
+      <c r="P13" s="5">
+        <v>2</v>
+      </c>
+      <c r="Q13" s="5">
+        <v>2</v>
+      </c>
+      <c r="R13" s="5">
+        <v>2</v>
+      </c>
+      <c r="S13" s="5">
+        <v>2</v>
+      </c>
+      <c r="T13" s="5">
+        <v>2</v>
+      </c>
+      <c r="U13" s="5">
+        <v>2</v>
+      </c>
+      <c r="V13" s="5">
+        <v>2</v>
+      </c>
+      <c r="W13" s="5">
+        <v>2</v>
+      </c>
+      <c r="X13" s="5">
+        <v>2</v>
+      </c>
+      <c r="Y13" s="5">
+        <v>2</v>
+      </c>
+      <c r="Z13" s="5">
         <v>2</v>
       </c>
       <c r="AB13" s="3">
@@ -6272,83 +6272,83 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:36" ht="18" x14ac:dyDescent="0.4">
-      <c r="A14" s="6" t="s">
+    <row r="14" spans="1:36" ht="18" x14ac:dyDescent="0.35">
+      <c r="A14" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="B14" s="6">
-        <v>0</v>
-      </c>
-      <c r="C14" s="6">
-        <v>0</v>
-      </c>
-      <c r="D14" s="6">
-        <v>0</v>
-      </c>
-      <c r="E14" s="6">
-        <v>0</v>
-      </c>
-      <c r="F14" s="6">
-        <v>0</v>
-      </c>
-      <c r="G14" s="6">
-        <v>0</v>
-      </c>
-      <c r="H14" s="6">
-        <v>0</v>
-      </c>
-      <c r="I14" s="6">
-        <v>0</v>
-      </c>
-      <c r="J14" s="6">
-        <v>0</v>
-      </c>
-      <c r="K14" s="6">
-        <v>0</v>
-      </c>
-      <c r="L14" s="6">
-        <v>0</v>
-      </c>
-      <c r="M14" s="6">
-        <v>0</v>
-      </c>
-      <c r="N14" s="6">
+      <c r="B14" s="5">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5">
+        <v>0</v>
+      </c>
+      <c r="D14" s="5">
+        <v>0</v>
+      </c>
+      <c r="E14" s="5">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5">
+        <v>0</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5">
+        <v>0</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5">
+        <v>0</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
         <v>1</v>
       </c>
-      <c r="O14" s="6">
-        <v>2</v>
-      </c>
-      <c r="P14" s="6">
-        <v>2</v>
-      </c>
-      <c r="Q14" s="6">
-        <v>2</v>
-      </c>
-      <c r="R14" s="6">
-        <v>0</v>
-      </c>
-      <c r="S14" s="6">
-        <v>2</v>
-      </c>
-      <c r="T14" s="6">
-        <v>0</v>
-      </c>
-      <c r="U14" s="6">
-        <v>2</v>
-      </c>
-      <c r="V14" s="6">
-        <v>2</v>
-      </c>
-      <c r="W14" s="6">
-        <v>2</v>
-      </c>
-      <c r="X14" s="6">
-        <v>2</v>
-      </c>
-      <c r="Y14" s="6">
-        <v>2</v>
-      </c>
-      <c r="Z14" s="6">
+      <c r="O14" s="5">
+        <v>2</v>
+      </c>
+      <c r="P14" s="5">
+        <v>2</v>
+      </c>
+      <c r="Q14" s="5">
+        <v>2</v>
+      </c>
+      <c r="R14" s="5">
+        <v>0</v>
+      </c>
+      <c r="S14" s="5">
+        <v>2</v>
+      </c>
+      <c r="T14" s="5">
+        <v>0</v>
+      </c>
+      <c r="U14" s="5">
+        <v>2</v>
+      </c>
+      <c r="V14" s="5">
+        <v>2</v>
+      </c>
+      <c r="W14" s="5">
+        <v>2</v>
+      </c>
+      <c r="X14" s="5">
+        <v>2</v>
+      </c>
+      <c r="Y14" s="5">
+        <v>2</v>
+      </c>
+      <c r="Z14" s="5">
         <v>2</v>
       </c>
       <c r="AB14" s="3">
@@ -6379,83 +6379,83 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:36" ht="18" x14ac:dyDescent="0.4">
-      <c r="A15" s="6" t="s">
+    <row r="15" spans="1:36" ht="18" x14ac:dyDescent="0.35">
+      <c r="A15" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="B15" s="6">
-        <v>0</v>
-      </c>
-      <c r="C15" s="6">
-        <v>0</v>
-      </c>
-      <c r="D15" s="6">
-        <v>0</v>
-      </c>
-      <c r="E15" s="6">
-        <v>0</v>
-      </c>
-      <c r="F15" s="6">
-        <v>0</v>
-      </c>
-      <c r="G15" s="6">
-        <v>0</v>
-      </c>
-      <c r="H15" s="6">
-        <v>0</v>
-      </c>
-      <c r="I15" s="6">
-        <v>0</v>
-      </c>
-      <c r="J15" s="6">
-        <v>0</v>
-      </c>
-      <c r="K15" s="6">
-        <v>0</v>
-      </c>
-      <c r="L15" s="6">
-        <v>0</v>
-      </c>
-      <c r="M15" s="6">
-        <v>0</v>
-      </c>
-      <c r="N15" s="6">
-        <v>0</v>
-      </c>
-      <c r="O15" s="6">
+      <c r="B15" s="5">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5">
+        <v>0</v>
+      </c>
+      <c r="E15" s="5">
+        <v>0</v>
+      </c>
+      <c r="F15" s="5">
+        <v>0</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5">
+        <v>0</v>
+      </c>
+      <c r="I15" s="5">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <v>0</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>0</v>
+      </c>
+      <c r="O15" s="5">
         <v>1</v>
       </c>
-      <c r="P15" s="6">
-        <v>2</v>
-      </c>
-      <c r="Q15" s="6">
-        <v>2</v>
-      </c>
-      <c r="R15" s="6">
-        <v>0</v>
-      </c>
-      <c r="S15" s="6">
-        <v>2</v>
-      </c>
-      <c r="T15" s="6">
-        <v>0</v>
-      </c>
-      <c r="U15" s="6">
-        <v>2</v>
-      </c>
-      <c r="V15" s="6">
-        <v>2</v>
-      </c>
-      <c r="W15" s="6">
-        <v>2</v>
-      </c>
-      <c r="X15" s="6">
-        <v>2</v>
-      </c>
-      <c r="Y15" s="6">
-        <v>2</v>
-      </c>
-      <c r="Z15" s="6">
+      <c r="P15" s="5">
+        <v>2</v>
+      </c>
+      <c r="Q15" s="5">
+        <v>2</v>
+      </c>
+      <c r="R15" s="5">
+        <v>0</v>
+      </c>
+      <c r="S15" s="5">
+        <v>2</v>
+      </c>
+      <c r="T15" s="5">
+        <v>0</v>
+      </c>
+      <c r="U15" s="5">
+        <v>2</v>
+      </c>
+      <c r="V15" s="5">
+        <v>2</v>
+      </c>
+      <c r="W15" s="5">
+        <v>2</v>
+      </c>
+      <c r="X15" s="5">
+        <v>2</v>
+      </c>
+      <c r="Y15" s="5">
+        <v>2</v>
+      </c>
+      <c r="Z15" s="5">
         <v>2</v>
       </c>
       <c r="AB15" s="3">
@@ -6486,83 +6486,83 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:36" ht="18" x14ac:dyDescent="0.4">
-      <c r="A16" s="6" t="s">
+    <row r="16" spans="1:36" ht="18" x14ac:dyDescent="0.35">
+      <c r="A16" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="B16" s="6">
-        <v>0</v>
-      </c>
-      <c r="C16" s="6">
-        <v>0</v>
-      </c>
-      <c r="D16" s="6">
-        <v>0</v>
-      </c>
-      <c r="E16" s="6">
-        <v>0</v>
-      </c>
-      <c r="F16" s="6">
-        <v>0</v>
-      </c>
-      <c r="G16" s="6">
-        <v>0</v>
-      </c>
-      <c r="H16" s="6">
-        <v>0</v>
-      </c>
-      <c r="I16" s="6">
-        <v>0</v>
-      </c>
-      <c r="J16" s="6">
-        <v>0</v>
-      </c>
-      <c r="K16" s="6">
-        <v>0</v>
-      </c>
-      <c r="L16" s="6">
-        <v>0</v>
-      </c>
-      <c r="M16" s="6">
-        <v>0</v>
-      </c>
-      <c r="N16" s="6">
-        <v>0</v>
-      </c>
-      <c r="O16" s="6">
-        <v>0</v>
-      </c>
-      <c r="P16" s="6">
+      <c r="B16" s="5">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5">
+        <v>0</v>
+      </c>
+      <c r="D16" s="5">
+        <v>0</v>
+      </c>
+      <c r="E16" s="5">
+        <v>0</v>
+      </c>
+      <c r="F16" s="5">
+        <v>0</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5">
+        <v>0</v>
+      </c>
+      <c r="I16" s="5">
+        <v>0</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>0</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>0</v>
+      </c>
+      <c r="O16" s="5">
+        <v>0</v>
+      </c>
+      <c r="P16" s="5">
         <v>1</v>
       </c>
-      <c r="Q16" s="6">
-        <v>2</v>
-      </c>
-      <c r="R16" s="6">
-        <v>0</v>
-      </c>
-      <c r="S16" s="6">
-        <v>2</v>
-      </c>
-      <c r="T16" s="6">
-        <v>0</v>
-      </c>
-      <c r="U16" s="6">
-        <v>2</v>
-      </c>
-      <c r="V16" s="6">
-        <v>2</v>
-      </c>
-      <c r="W16" s="6">
-        <v>2</v>
-      </c>
-      <c r="X16" s="6">
-        <v>2</v>
-      </c>
-      <c r="Y16" s="6">
-        <v>2</v>
-      </c>
-      <c r="Z16" s="6">
+      <c r="Q16" s="5">
+        <v>2</v>
+      </c>
+      <c r="R16" s="5">
+        <v>0</v>
+      </c>
+      <c r="S16" s="5">
+        <v>2</v>
+      </c>
+      <c r="T16" s="5">
+        <v>0</v>
+      </c>
+      <c r="U16" s="5">
+        <v>2</v>
+      </c>
+      <c r="V16" s="5">
+        <v>2</v>
+      </c>
+      <c r="W16" s="5">
+        <v>2</v>
+      </c>
+      <c r="X16" s="5">
+        <v>2</v>
+      </c>
+      <c r="Y16" s="5">
+        <v>2</v>
+      </c>
+      <c r="Z16" s="5">
         <v>2</v>
       </c>
       <c r="AB16" s="3">
@@ -6593,83 +6593,83 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:36" ht="18" x14ac:dyDescent="0.4">
-      <c r="A17" s="6" t="s">
+    <row r="17" spans="1:36" ht="18" x14ac:dyDescent="0.35">
+      <c r="A17" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="B17" s="6">
-        <v>0</v>
-      </c>
-      <c r="C17" s="6">
-        <v>0</v>
-      </c>
-      <c r="D17" s="6">
-        <v>0</v>
-      </c>
-      <c r="E17" s="6">
-        <v>0</v>
-      </c>
-      <c r="F17" s="6">
-        <v>0</v>
-      </c>
-      <c r="G17" s="6">
-        <v>0</v>
-      </c>
-      <c r="H17" s="6">
-        <v>0</v>
-      </c>
-      <c r="I17" s="6">
-        <v>0</v>
-      </c>
-      <c r="J17" s="6">
-        <v>0</v>
-      </c>
-      <c r="K17" s="6">
-        <v>0</v>
-      </c>
-      <c r="L17" s="6">
-        <v>0</v>
-      </c>
-      <c r="M17" s="6">
-        <v>0</v>
-      </c>
-      <c r="N17" s="6">
-        <v>0</v>
-      </c>
-      <c r="O17" s="6">
-        <v>0</v>
-      </c>
-      <c r="P17" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="6">
+      <c r="B17" s="5">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5">
+        <v>0</v>
+      </c>
+      <c r="D17" s="5">
+        <v>0</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5">
+        <v>0</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>0</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>0</v>
+      </c>
+      <c r="O17" s="5">
+        <v>0</v>
+      </c>
+      <c r="P17" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="5">
         <v>1</v>
       </c>
-      <c r="R17" s="6">
-        <v>0</v>
-      </c>
-      <c r="S17" s="6">
-        <v>2</v>
-      </c>
-      <c r="T17" s="6">
-        <v>0</v>
-      </c>
-      <c r="U17" s="6">
-        <v>2</v>
-      </c>
-      <c r="V17" s="6">
-        <v>2</v>
-      </c>
-      <c r="W17" s="6">
-        <v>2</v>
-      </c>
-      <c r="X17" s="6">
-        <v>2</v>
-      </c>
-      <c r="Y17" s="6">
-        <v>2</v>
-      </c>
-      <c r="Z17" s="6">
+      <c r="R17" s="5">
+        <v>0</v>
+      </c>
+      <c r="S17" s="5">
+        <v>2</v>
+      </c>
+      <c r="T17" s="5">
+        <v>0</v>
+      </c>
+      <c r="U17" s="5">
+        <v>2</v>
+      </c>
+      <c r="V17" s="5">
+        <v>2</v>
+      </c>
+      <c r="W17" s="5">
+        <v>2</v>
+      </c>
+      <c r="X17" s="5">
+        <v>2</v>
+      </c>
+      <c r="Y17" s="5">
+        <v>2</v>
+      </c>
+      <c r="Z17" s="5">
         <v>2</v>
       </c>
       <c r="AB17" s="3">
@@ -6700,83 +6700,83 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:36" ht="18" x14ac:dyDescent="0.4">
-      <c r="A18" s="6" t="s">
+    <row r="18" spans="1:36" ht="18" x14ac:dyDescent="0.35">
+      <c r="A18" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="B18" s="6">
-        <v>2</v>
-      </c>
-      <c r="C18" s="6">
-        <v>2</v>
-      </c>
-      <c r="D18" s="6">
-        <v>2</v>
-      </c>
-      <c r="E18" s="6">
-        <v>2</v>
-      </c>
-      <c r="F18" s="6">
-        <v>0</v>
-      </c>
-      <c r="G18" s="6">
-        <v>0</v>
-      </c>
-      <c r="H18" s="6">
-        <v>2</v>
-      </c>
-      <c r="I18" s="6">
-        <v>2</v>
-      </c>
-      <c r="J18" s="6">
-        <v>2</v>
-      </c>
-      <c r="K18" s="6">
-        <v>2</v>
-      </c>
-      <c r="L18" s="6">
-        <v>2</v>
-      </c>
-      <c r="M18" s="6">
-        <v>0</v>
-      </c>
-      <c r="N18" s="6">
-        <v>2</v>
-      </c>
-      <c r="O18" s="6">
-        <v>2</v>
-      </c>
-      <c r="P18" s="6">
-        <v>2</v>
-      </c>
-      <c r="Q18" s="6">
-        <v>2</v>
-      </c>
-      <c r="R18" s="6">
+      <c r="B18" s="5">
+        <v>2</v>
+      </c>
+      <c r="C18" s="5">
+        <v>2</v>
+      </c>
+      <c r="D18" s="5">
+        <v>2</v>
+      </c>
+      <c r="E18" s="5">
+        <v>2</v>
+      </c>
+      <c r="F18" s="5">
+        <v>0</v>
+      </c>
+      <c r="G18" s="5">
+        <v>0</v>
+      </c>
+      <c r="H18" s="5">
+        <v>2</v>
+      </c>
+      <c r="I18" s="5">
+        <v>2</v>
+      </c>
+      <c r="J18" s="5">
+        <v>2</v>
+      </c>
+      <c r="K18" s="5">
+        <v>2</v>
+      </c>
+      <c r="L18" s="5">
+        <v>2</v>
+      </c>
+      <c r="M18" s="5">
+        <v>0</v>
+      </c>
+      <c r="N18" s="5">
+        <v>2</v>
+      </c>
+      <c r="O18" s="5">
+        <v>2</v>
+      </c>
+      <c r="P18" s="5">
+        <v>2</v>
+      </c>
+      <c r="Q18" s="5">
+        <v>2</v>
+      </c>
+      <c r="R18" s="5">
         <v>1</v>
       </c>
-      <c r="S18" s="6">
-        <v>2</v>
-      </c>
-      <c r="T18" s="6">
-        <v>2</v>
-      </c>
-      <c r="U18" s="6">
-        <v>2</v>
-      </c>
-      <c r="V18" s="6">
-        <v>2</v>
-      </c>
-      <c r="W18" s="6">
-        <v>2</v>
-      </c>
-      <c r="X18" s="6">
-        <v>2</v>
-      </c>
-      <c r="Y18" s="6">
-        <v>2</v>
-      </c>
-      <c r="Z18" s="6">
+      <c r="S18" s="5">
+        <v>2</v>
+      </c>
+      <c r="T18" s="5">
+        <v>2</v>
+      </c>
+      <c r="U18" s="5">
+        <v>2</v>
+      </c>
+      <c r="V18" s="5">
+        <v>2</v>
+      </c>
+      <c r="W18" s="5">
+        <v>2</v>
+      </c>
+      <c r="X18" s="5">
+        <v>2</v>
+      </c>
+      <c r="Y18" s="5">
+        <v>2</v>
+      </c>
+      <c r="Z18" s="5">
         <v>2</v>
       </c>
       <c r="AB18" s="3">
@@ -6807,83 +6807,83 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:36" ht="18" x14ac:dyDescent="0.4">
-      <c r="A19" s="6" t="s">
+    <row r="19" spans="1:36" ht="18" x14ac:dyDescent="0.35">
+      <c r="A19" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="B19" s="6">
-        <v>0</v>
-      </c>
-      <c r="C19" s="6">
-        <v>0</v>
-      </c>
-      <c r="D19" s="6">
-        <v>0</v>
-      </c>
-      <c r="E19" s="6">
-        <v>0</v>
-      </c>
-      <c r="F19" s="6">
-        <v>0</v>
-      </c>
-      <c r="G19" s="6">
-        <v>0</v>
-      </c>
-      <c r="H19" s="6">
-        <v>0</v>
-      </c>
-      <c r="I19" s="6">
-        <v>0</v>
-      </c>
-      <c r="J19" s="6">
-        <v>0</v>
-      </c>
-      <c r="K19" s="6">
-        <v>0</v>
-      </c>
-      <c r="L19" s="6">
-        <v>0</v>
-      </c>
-      <c r="M19" s="6">
-        <v>0</v>
-      </c>
-      <c r="N19" s="6">
-        <v>0</v>
-      </c>
-      <c r="O19" s="6">
-        <v>0</v>
-      </c>
-      <c r="P19" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="6">
-        <v>0</v>
-      </c>
-      <c r="R19" s="6">
-        <v>0</v>
-      </c>
-      <c r="S19" s="6">
+      <c r="B19" s="5">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5">
+        <v>0</v>
+      </c>
+      <c r="D19" s="5">
+        <v>0</v>
+      </c>
+      <c r="E19" s="5">
+        <v>0</v>
+      </c>
+      <c r="F19" s="5">
+        <v>0</v>
+      </c>
+      <c r="G19" s="5">
+        <v>0</v>
+      </c>
+      <c r="H19" s="5">
+        <v>0</v>
+      </c>
+      <c r="I19" s="5">
+        <v>0</v>
+      </c>
+      <c r="J19" s="5">
+        <v>0</v>
+      </c>
+      <c r="K19" s="5">
+        <v>0</v>
+      </c>
+      <c r="L19" s="5">
+        <v>0</v>
+      </c>
+      <c r="M19" s="5">
+        <v>0</v>
+      </c>
+      <c r="N19" s="5">
+        <v>0</v>
+      </c>
+      <c r="O19" s="5">
+        <v>0</v>
+      </c>
+      <c r="P19" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="5">
+        <v>0</v>
+      </c>
+      <c r="R19" s="5">
+        <v>0</v>
+      </c>
+      <c r="S19" s="5">
         <v>1</v>
       </c>
-      <c r="T19" s="6">
-        <v>0</v>
-      </c>
-      <c r="U19" s="6">
-        <v>2</v>
-      </c>
-      <c r="V19" s="6">
-        <v>2</v>
-      </c>
-      <c r="W19" s="6">
-        <v>2</v>
-      </c>
-      <c r="X19" s="6">
-        <v>2</v>
-      </c>
-      <c r="Y19" s="6">
-        <v>2</v>
-      </c>
-      <c r="Z19" s="6">
+      <c r="T19" s="5">
+        <v>0</v>
+      </c>
+      <c r="U19" s="5">
+        <v>2</v>
+      </c>
+      <c r="V19" s="5">
+        <v>2</v>
+      </c>
+      <c r="W19" s="5">
+        <v>2</v>
+      </c>
+      <c r="X19" s="5">
+        <v>2</v>
+      </c>
+      <c r="Y19" s="5">
+        <v>2</v>
+      </c>
+      <c r="Z19" s="5">
         <v>2</v>
       </c>
       <c r="AB19" s="3">
@@ -6914,83 +6914,83 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:36" ht="18" x14ac:dyDescent="0.4">
-      <c r="A20" s="6" t="s">
+    <row r="20" spans="1:36" ht="18" x14ac:dyDescent="0.35">
+      <c r="A20" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="B20" s="6">
-        <v>2</v>
-      </c>
-      <c r="C20" s="6">
-        <v>2</v>
-      </c>
-      <c r="D20" s="6">
-        <v>2</v>
-      </c>
-      <c r="E20" s="6">
-        <v>2</v>
-      </c>
-      <c r="F20" s="6">
-        <v>0</v>
-      </c>
-      <c r="G20" s="6">
-        <v>0</v>
-      </c>
-      <c r="H20" s="6">
-        <v>2</v>
-      </c>
-      <c r="I20" s="6">
-        <v>2</v>
-      </c>
-      <c r="J20" s="6">
-        <v>2</v>
-      </c>
-      <c r="K20" s="6">
-        <v>2</v>
-      </c>
-      <c r="L20" s="6">
-        <v>2</v>
-      </c>
-      <c r="M20" s="6">
-        <v>0</v>
-      </c>
-      <c r="N20" s="6">
-        <v>2</v>
-      </c>
-      <c r="O20" s="6">
-        <v>2</v>
-      </c>
-      <c r="P20" s="6">
-        <v>2</v>
-      </c>
-      <c r="Q20" s="6">
-        <v>2</v>
-      </c>
-      <c r="R20" s="6">
-        <v>0</v>
-      </c>
-      <c r="S20" s="6">
-        <v>2</v>
-      </c>
-      <c r="T20" s="6">
+      <c r="B20" s="5">
+        <v>2</v>
+      </c>
+      <c r="C20" s="5">
+        <v>2</v>
+      </c>
+      <c r="D20" s="5">
+        <v>2</v>
+      </c>
+      <c r="E20" s="5">
+        <v>2</v>
+      </c>
+      <c r="F20" s="5">
+        <v>0</v>
+      </c>
+      <c r="G20" s="5">
+        <v>0</v>
+      </c>
+      <c r="H20" s="5">
+        <v>2</v>
+      </c>
+      <c r="I20" s="5">
+        <v>2</v>
+      </c>
+      <c r="J20" s="5">
+        <v>2</v>
+      </c>
+      <c r="K20" s="5">
+        <v>2</v>
+      </c>
+      <c r="L20" s="5">
+        <v>2</v>
+      </c>
+      <c r="M20" s="5">
+        <v>0</v>
+      </c>
+      <c r="N20" s="5">
+        <v>2</v>
+      </c>
+      <c r="O20" s="5">
+        <v>2</v>
+      </c>
+      <c r="P20" s="5">
+        <v>2</v>
+      </c>
+      <c r="Q20" s="5">
+        <v>2</v>
+      </c>
+      <c r="R20" s="5">
+        <v>0</v>
+      </c>
+      <c r="S20" s="5">
+        <v>2</v>
+      </c>
+      <c r="T20" s="5">
         <v>1</v>
       </c>
-      <c r="U20" s="6">
-        <v>2</v>
-      </c>
-      <c r="V20" s="6">
-        <v>2</v>
-      </c>
-      <c r="W20" s="6">
-        <v>2</v>
-      </c>
-      <c r="X20" s="6">
-        <v>2</v>
-      </c>
-      <c r="Y20" s="6">
-        <v>2</v>
-      </c>
-      <c r="Z20" s="6">
+      <c r="U20" s="5">
+        <v>2</v>
+      </c>
+      <c r="V20" s="5">
+        <v>2</v>
+      </c>
+      <c r="W20" s="5">
+        <v>2</v>
+      </c>
+      <c r="X20" s="5">
+        <v>2</v>
+      </c>
+      <c r="Y20" s="5">
+        <v>2</v>
+      </c>
+      <c r="Z20" s="5">
         <v>2</v>
       </c>
       <c r="AB20" s="3">
@@ -7021,83 +7021,83 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:36" ht="18" x14ac:dyDescent="0.4">
-      <c r="A21" s="6" t="s">
+    <row r="21" spans="1:36" ht="18" x14ac:dyDescent="0.35">
+      <c r="A21" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="B21" s="6">
-        <v>0</v>
-      </c>
-      <c r="C21" s="6">
-        <v>0</v>
-      </c>
-      <c r="D21" s="6">
-        <v>0</v>
-      </c>
-      <c r="E21" s="6">
-        <v>0</v>
-      </c>
-      <c r="F21" s="6">
-        <v>0</v>
-      </c>
-      <c r="G21" s="6">
-        <v>0</v>
-      </c>
-      <c r="H21" s="6">
-        <v>0</v>
-      </c>
-      <c r="I21" s="6">
-        <v>0</v>
-      </c>
-      <c r="J21" s="6">
-        <v>0</v>
-      </c>
-      <c r="K21" s="6">
-        <v>0</v>
-      </c>
-      <c r="L21" s="6">
-        <v>0</v>
-      </c>
-      <c r="M21" s="6">
-        <v>0</v>
-      </c>
-      <c r="N21" s="6">
-        <v>0</v>
-      </c>
-      <c r="O21" s="6">
-        <v>0</v>
-      </c>
-      <c r="P21" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="6">
-        <v>0</v>
-      </c>
-      <c r="R21" s="6">
-        <v>0</v>
-      </c>
-      <c r="S21" s="6">
-        <v>0</v>
-      </c>
-      <c r="T21" s="6">
-        <v>0</v>
-      </c>
-      <c r="U21" s="6">
+      <c r="B21" s="5">
+        <v>0</v>
+      </c>
+      <c r="C21" s="5">
+        <v>0</v>
+      </c>
+      <c r="D21" s="5">
+        <v>0</v>
+      </c>
+      <c r="E21" s="5">
+        <v>0</v>
+      </c>
+      <c r="F21" s="5">
+        <v>0</v>
+      </c>
+      <c r="G21" s="5">
+        <v>0</v>
+      </c>
+      <c r="H21" s="5">
+        <v>0</v>
+      </c>
+      <c r="I21" s="5">
+        <v>0</v>
+      </c>
+      <c r="J21" s="5">
+        <v>0</v>
+      </c>
+      <c r="K21" s="5">
+        <v>0</v>
+      </c>
+      <c r="L21" s="5">
+        <v>0</v>
+      </c>
+      <c r="M21" s="5">
+        <v>0</v>
+      </c>
+      <c r="N21" s="5">
+        <v>0</v>
+      </c>
+      <c r="O21" s="5">
+        <v>0</v>
+      </c>
+      <c r="P21" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="5">
+        <v>0</v>
+      </c>
+      <c r="R21" s="5">
+        <v>0</v>
+      </c>
+      <c r="S21" s="5">
+        <v>0</v>
+      </c>
+      <c r="T21" s="5">
+        <v>0</v>
+      </c>
+      <c r="U21" s="5">
         <v>1</v>
       </c>
-      <c r="V21" s="6">
-        <v>2</v>
-      </c>
-      <c r="W21" s="6">
-        <v>2</v>
-      </c>
-      <c r="X21" s="6">
-        <v>2</v>
-      </c>
-      <c r="Y21" s="6">
-        <v>2</v>
-      </c>
-      <c r="Z21" s="6">
+      <c r="V21" s="5">
+        <v>2</v>
+      </c>
+      <c r="W21" s="5">
+        <v>2</v>
+      </c>
+      <c r="X21" s="5">
+        <v>2</v>
+      </c>
+      <c r="Y21" s="5">
+        <v>2</v>
+      </c>
+      <c r="Z21" s="5">
         <v>2</v>
       </c>
       <c r="AB21" s="3">
@@ -7128,83 +7128,83 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:36" ht="18" x14ac:dyDescent="0.4">
-      <c r="A22" s="6" t="s">
+    <row r="22" spans="1:36" ht="18" x14ac:dyDescent="0.35">
+      <c r="A22" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="B22" s="6">
-        <v>0</v>
-      </c>
-      <c r="C22" s="6">
-        <v>0</v>
-      </c>
-      <c r="D22" s="6">
-        <v>0</v>
-      </c>
-      <c r="E22" s="6">
-        <v>0</v>
-      </c>
-      <c r="F22" s="6">
-        <v>0</v>
-      </c>
-      <c r="G22" s="6">
-        <v>0</v>
-      </c>
-      <c r="H22" s="6">
-        <v>0</v>
-      </c>
-      <c r="I22" s="6">
-        <v>0</v>
-      </c>
-      <c r="J22" s="6">
-        <v>0</v>
-      </c>
-      <c r="K22" s="6">
-        <v>0</v>
-      </c>
-      <c r="L22" s="6">
-        <v>0</v>
-      </c>
-      <c r="M22" s="6">
-        <v>0</v>
-      </c>
-      <c r="N22" s="6">
-        <v>0</v>
-      </c>
-      <c r="O22" s="6">
-        <v>0</v>
-      </c>
-      <c r="P22" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="6">
-        <v>0</v>
-      </c>
-      <c r="R22" s="6">
-        <v>0</v>
-      </c>
-      <c r="S22" s="6">
-        <v>0</v>
-      </c>
-      <c r="T22" s="6">
-        <v>0</v>
-      </c>
-      <c r="U22" s="6">
-        <v>0</v>
-      </c>
-      <c r="V22" s="6">
+      <c r="B22" s="5">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5">
+        <v>0</v>
+      </c>
+      <c r="D22" s="5">
+        <v>0</v>
+      </c>
+      <c r="E22" s="5">
+        <v>0</v>
+      </c>
+      <c r="F22" s="5">
+        <v>0</v>
+      </c>
+      <c r="G22" s="5">
+        <v>0</v>
+      </c>
+      <c r="H22" s="5">
+        <v>0</v>
+      </c>
+      <c r="I22" s="5">
+        <v>0</v>
+      </c>
+      <c r="J22" s="5">
+        <v>0</v>
+      </c>
+      <c r="K22" s="5">
+        <v>0</v>
+      </c>
+      <c r="L22" s="5">
+        <v>0</v>
+      </c>
+      <c r="M22" s="5">
+        <v>0</v>
+      </c>
+      <c r="N22" s="5">
+        <v>0</v>
+      </c>
+      <c r="O22" s="5">
+        <v>0</v>
+      </c>
+      <c r="P22" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="5">
+        <v>0</v>
+      </c>
+      <c r="R22" s="5">
+        <v>0</v>
+      </c>
+      <c r="S22" s="5">
+        <v>0</v>
+      </c>
+      <c r="T22" s="5">
+        <v>0</v>
+      </c>
+      <c r="U22" s="5">
+        <v>0</v>
+      </c>
+      <c r="V22" s="5">
         <v>1</v>
       </c>
-      <c r="W22" s="6">
-        <v>2</v>
-      </c>
-      <c r="X22" s="6">
-        <v>2</v>
-      </c>
-      <c r="Y22" s="6">
-        <v>2</v>
-      </c>
-      <c r="Z22" s="6">
+      <c r="W22" s="5">
+        <v>2</v>
+      </c>
+      <c r="X22" s="5">
+        <v>2</v>
+      </c>
+      <c r="Y22" s="5">
+        <v>2</v>
+      </c>
+      <c r="Z22" s="5">
         <v>2</v>
       </c>
       <c r="AB22" s="3">
@@ -7235,83 +7235,83 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:36" ht="18" x14ac:dyDescent="0.4">
-      <c r="A23" s="6" t="s">
+    <row r="23" spans="1:36" ht="18" x14ac:dyDescent="0.35">
+      <c r="A23" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="B23" s="6">
-        <v>0</v>
-      </c>
-      <c r="C23" s="6">
-        <v>0</v>
-      </c>
-      <c r="D23" s="6">
-        <v>0</v>
-      </c>
-      <c r="E23" s="6">
-        <v>0</v>
-      </c>
-      <c r="F23" s="6">
-        <v>0</v>
-      </c>
-      <c r="G23" s="6">
-        <v>0</v>
-      </c>
-      <c r="H23" s="6">
-        <v>0</v>
-      </c>
-      <c r="I23" s="6">
-        <v>0</v>
-      </c>
-      <c r="J23" s="6">
-        <v>0</v>
-      </c>
-      <c r="K23" s="6">
-        <v>0</v>
-      </c>
-      <c r="L23" s="6">
-        <v>0</v>
-      </c>
-      <c r="M23" s="6">
-        <v>0</v>
-      </c>
-      <c r="N23" s="6">
-        <v>0</v>
-      </c>
-      <c r="O23" s="6">
-        <v>0</v>
-      </c>
-      <c r="P23" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="6">
-        <v>0</v>
-      </c>
-      <c r="R23" s="6">
-        <v>0</v>
-      </c>
-      <c r="S23" s="6">
-        <v>0</v>
-      </c>
-      <c r="T23" s="6">
-        <v>0</v>
-      </c>
-      <c r="U23" s="6">
-        <v>0</v>
-      </c>
-      <c r="V23" s="6">
-        <v>0</v>
-      </c>
-      <c r="W23" s="6">
+      <c r="B23" s="5">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5">
+        <v>0</v>
+      </c>
+      <c r="D23" s="5">
+        <v>0</v>
+      </c>
+      <c r="E23" s="5">
+        <v>0</v>
+      </c>
+      <c r="F23" s="5">
+        <v>0</v>
+      </c>
+      <c r="G23" s="5">
+        <v>0</v>
+      </c>
+      <c r="H23" s="5">
+        <v>0</v>
+      </c>
+      <c r="I23" s="5">
+        <v>0</v>
+      </c>
+      <c r="J23" s="5">
+        <v>0</v>
+      </c>
+      <c r="K23" s="5">
+        <v>0</v>
+      </c>
+      <c r="L23" s="5">
+        <v>0</v>
+      </c>
+      <c r="M23" s="5">
+        <v>0</v>
+      </c>
+      <c r="N23" s="5">
+        <v>0</v>
+      </c>
+      <c r="O23" s="5">
+        <v>0</v>
+      </c>
+      <c r="P23" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="5">
+        <v>0</v>
+      </c>
+      <c r="R23" s="5">
+        <v>0</v>
+      </c>
+      <c r="S23" s="5">
+        <v>0</v>
+      </c>
+      <c r="T23" s="5">
+        <v>0</v>
+      </c>
+      <c r="U23" s="5">
+        <v>0</v>
+      </c>
+      <c r="V23" s="5">
+        <v>0</v>
+      </c>
+      <c r="W23" s="5">
         <v>1</v>
       </c>
-      <c r="X23" s="6">
-        <v>2</v>
-      </c>
-      <c r="Y23" s="6">
-        <v>2</v>
-      </c>
-      <c r="Z23" s="6">
+      <c r="X23" s="5">
+        <v>2</v>
+      </c>
+      <c r="Y23" s="5">
+        <v>2</v>
+      </c>
+      <c r="Z23" s="5">
         <v>2</v>
       </c>
       <c r="AB23" s="3">
@@ -7342,83 +7342,83 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:36" ht="18" x14ac:dyDescent="0.4">
-      <c r="A24" s="6" t="s">
+    <row r="24" spans="1:36" ht="18" x14ac:dyDescent="0.35">
+      <c r="A24" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="B24" s="6">
-        <v>0</v>
-      </c>
-      <c r="C24" s="6">
-        <v>0</v>
-      </c>
-      <c r="D24" s="6">
-        <v>0</v>
-      </c>
-      <c r="E24" s="6">
-        <v>0</v>
-      </c>
-      <c r="F24" s="6">
-        <v>0</v>
-      </c>
-      <c r="G24" s="6">
-        <v>0</v>
-      </c>
-      <c r="H24" s="6">
-        <v>0</v>
-      </c>
-      <c r="I24" s="6">
-        <v>0</v>
-      </c>
-      <c r="J24" s="6">
-        <v>0</v>
-      </c>
-      <c r="K24" s="6">
-        <v>0</v>
-      </c>
-      <c r="L24" s="6">
-        <v>0</v>
-      </c>
-      <c r="M24" s="6">
-        <v>0</v>
-      </c>
-      <c r="N24" s="6">
-        <v>0</v>
-      </c>
-      <c r="O24" s="6">
-        <v>0</v>
-      </c>
-      <c r="P24" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="6">
-        <v>0</v>
-      </c>
-      <c r="R24" s="6">
-        <v>0</v>
-      </c>
-      <c r="S24" s="6">
-        <v>0</v>
-      </c>
-      <c r="T24" s="6">
-        <v>0</v>
-      </c>
-      <c r="U24" s="6">
-        <v>0</v>
-      </c>
-      <c r="V24" s="6">
-        <v>0</v>
-      </c>
-      <c r="W24" s="6">
-        <v>0</v>
-      </c>
-      <c r="X24" s="6">
+      <c r="B24" s="5">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5">
+        <v>0</v>
+      </c>
+      <c r="D24" s="5">
+        <v>0</v>
+      </c>
+      <c r="E24" s="5">
+        <v>0</v>
+      </c>
+      <c r="F24" s="5">
+        <v>0</v>
+      </c>
+      <c r="G24" s="5">
+        <v>0</v>
+      </c>
+      <c r="H24" s="5">
+        <v>0</v>
+      </c>
+      <c r="I24" s="5">
+        <v>0</v>
+      </c>
+      <c r="J24" s="5">
+        <v>0</v>
+      </c>
+      <c r="K24" s="5">
+        <v>0</v>
+      </c>
+      <c r="L24" s="5">
+        <v>0</v>
+      </c>
+      <c r="M24" s="5">
+        <v>0</v>
+      </c>
+      <c r="N24" s="5">
+        <v>0</v>
+      </c>
+      <c r="O24" s="5">
+        <v>0</v>
+      </c>
+      <c r="P24" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="5">
+        <v>0</v>
+      </c>
+      <c r="R24" s="5">
+        <v>0</v>
+      </c>
+      <c r="S24" s="5">
+        <v>0</v>
+      </c>
+      <c r="T24" s="5">
+        <v>0</v>
+      </c>
+      <c r="U24" s="5">
+        <v>0</v>
+      </c>
+      <c r="V24" s="5">
+        <v>0</v>
+      </c>
+      <c r="W24" s="5">
+        <v>0</v>
+      </c>
+      <c r="X24" s="5">
         <v>1</v>
       </c>
-      <c r="Y24" s="6">
-        <v>2</v>
-      </c>
-      <c r="Z24" s="6">
+      <c r="Y24" s="5">
+        <v>2</v>
+      </c>
+      <c r="Z24" s="5">
         <v>2</v>
       </c>
       <c r="AB24" s="3">
@@ -7449,83 +7449,83 @@
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:36" ht="18" x14ac:dyDescent="0.4">
-      <c r="A25" s="6" t="s">
+    <row r="25" spans="1:36" ht="18" x14ac:dyDescent="0.35">
+      <c r="A25" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="B25" s="6">
-        <v>0</v>
-      </c>
-      <c r="C25" s="6">
-        <v>0</v>
-      </c>
-      <c r="D25" s="6">
-        <v>0</v>
-      </c>
-      <c r="E25" s="6">
-        <v>0</v>
-      </c>
-      <c r="F25" s="6">
-        <v>0</v>
-      </c>
-      <c r="G25" s="6">
-        <v>0</v>
-      </c>
-      <c r="H25" s="6">
-        <v>0</v>
-      </c>
-      <c r="I25" s="6">
-        <v>0</v>
-      </c>
-      <c r="J25" s="6">
-        <v>0</v>
-      </c>
-      <c r="K25" s="6">
-        <v>0</v>
-      </c>
-      <c r="L25" s="6">
-        <v>0</v>
-      </c>
-      <c r="M25" s="6">
-        <v>0</v>
-      </c>
-      <c r="N25" s="6">
-        <v>0</v>
-      </c>
-      <c r="O25" s="6">
-        <v>0</v>
-      </c>
-      <c r="P25" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="6">
-        <v>0</v>
-      </c>
-      <c r="R25" s="6">
-        <v>0</v>
-      </c>
-      <c r="S25" s="6">
-        <v>0</v>
-      </c>
-      <c r="T25" s="6">
-        <v>0</v>
-      </c>
-      <c r="U25" s="6">
-        <v>0</v>
-      </c>
-      <c r="V25" s="6">
-        <v>0</v>
-      </c>
-      <c r="W25" s="6">
-        <v>0</v>
-      </c>
-      <c r="X25" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y25" s="6">
+      <c r="B25" s="5">
+        <v>0</v>
+      </c>
+      <c r="C25" s="5">
+        <v>0</v>
+      </c>
+      <c r="D25" s="5">
+        <v>0</v>
+      </c>
+      <c r="E25" s="5">
+        <v>0</v>
+      </c>
+      <c r="F25" s="5">
+        <v>0</v>
+      </c>
+      <c r="G25" s="5">
+        <v>0</v>
+      </c>
+      <c r="H25" s="5">
+        <v>0</v>
+      </c>
+      <c r="I25" s="5">
+        <v>0</v>
+      </c>
+      <c r="J25" s="5">
+        <v>0</v>
+      </c>
+      <c r="K25" s="5">
+        <v>0</v>
+      </c>
+      <c r="L25" s="5">
+        <v>0</v>
+      </c>
+      <c r="M25" s="5">
+        <v>0</v>
+      </c>
+      <c r="N25" s="5">
+        <v>0</v>
+      </c>
+      <c r="O25" s="5">
+        <v>0</v>
+      </c>
+      <c r="P25" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="5">
+        <v>0</v>
+      </c>
+      <c r="R25" s="5">
+        <v>0</v>
+      </c>
+      <c r="S25" s="5">
+        <v>0</v>
+      </c>
+      <c r="T25" s="5">
+        <v>0</v>
+      </c>
+      <c r="U25" s="5">
+        <v>0</v>
+      </c>
+      <c r="V25" s="5">
+        <v>0</v>
+      </c>
+      <c r="W25" s="5">
+        <v>0</v>
+      </c>
+      <c r="X25" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="5">
         <v>1</v>
       </c>
-      <c r="Z25" s="6">
+      <c r="Z25" s="5">
         <v>2</v>
       </c>
       <c r="AB25" s="3">
@@ -7556,83 +7556,83 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:36" ht="18" x14ac:dyDescent="0.4">
-      <c r="A26" s="6" t="s">
+    <row r="26" spans="1:36" ht="18" x14ac:dyDescent="0.35">
+      <c r="A26" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="B26" s="6">
-        <v>0</v>
-      </c>
-      <c r="C26" s="6">
-        <v>0</v>
-      </c>
-      <c r="D26" s="6">
-        <v>0</v>
-      </c>
-      <c r="E26" s="6">
-        <v>0</v>
-      </c>
-      <c r="F26" s="6">
-        <v>0</v>
-      </c>
-      <c r="G26" s="6">
-        <v>0</v>
-      </c>
-      <c r="H26" s="6">
-        <v>0</v>
-      </c>
-      <c r="I26" s="6">
-        <v>0</v>
-      </c>
-      <c r="J26" s="6">
-        <v>0</v>
-      </c>
-      <c r="K26" s="6">
-        <v>0</v>
-      </c>
-      <c r="L26" s="6">
-        <v>0</v>
-      </c>
-      <c r="M26" s="6">
-        <v>0</v>
-      </c>
-      <c r="N26" s="6">
-        <v>0</v>
-      </c>
-      <c r="O26" s="6">
-        <v>0</v>
-      </c>
-      <c r="P26" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="6">
-        <v>0</v>
-      </c>
-      <c r="R26" s="6">
-        <v>0</v>
-      </c>
-      <c r="S26" s="6">
-        <v>0</v>
-      </c>
-      <c r="T26" s="6">
-        <v>0</v>
-      </c>
-      <c r="U26" s="6">
-        <v>0</v>
-      </c>
-      <c r="V26" s="6">
-        <v>0</v>
-      </c>
-      <c r="W26" s="6">
-        <v>0</v>
-      </c>
-      <c r="X26" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y26" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z26" s="6">
+      <c r="B26" s="5">
+        <v>0</v>
+      </c>
+      <c r="C26" s="5">
+        <v>0</v>
+      </c>
+      <c r="D26" s="5">
+        <v>0</v>
+      </c>
+      <c r="E26" s="5">
+        <v>0</v>
+      </c>
+      <c r="F26" s="5">
+        <v>0</v>
+      </c>
+      <c r="G26" s="5">
+        <v>0</v>
+      </c>
+      <c r="H26" s="5">
+        <v>0</v>
+      </c>
+      <c r="I26" s="5">
+        <v>0</v>
+      </c>
+      <c r="J26" s="5">
+        <v>0</v>
+      </c>
+      <c r="K26" s="5">
+        <v>0</v>
+      </c>
+      <c r="L26" s="5">
+        <v>0</v>
+      </c>
+      <c r="M26" s="5">
+        <v>0</v>
+      </c>
+      <c r="N26" s="5">
+        <v>0</v>
+      </c>
+      <c r="O26" s="5">
+        <v>0</v>
+      </c>
+      <c r="P26" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="5">
+        <v>0</v>
+      </c>
+      <c r="R26" s="5">
+        <v>0</v>
+      </c>
+      <c r="S26" s="5">
+        <v>0</v>
+      </c>
+      <c r="T26" s="5">
+        <v>0</v>
+      </c>
+      <c r="U26" s="5">
+        <v>0</v>
+      </c>
+      <c r="V26" s="5">
+        <v>0</v>
+      </c>
+      <c r="W26" s="5">
+        <v>0</v>
+      </c>
+      <c r="X26" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z26" s="5">
         <v>1</v>
       </c>
       <c r="AB26" s="3">
@@ -7663,7 +7663,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:36" ht="18" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:36" ht="18" x14ac:dyDescent="0.35">
       <c r="AB27" s="3">
         <v>23</v>
       </c>
@@ -7692,7 +7692,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:36" ht="18" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:36" ht="18" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
         <v>69</v>
       </c>
@@ -7772,7 +7772,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="29" spans="1:36" ht="18" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:36" ht="18" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
         <v>86</v>
       </c>
@@ -7852,7 +7852,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:36" ht="18" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:36" ht="18" x14ac:dyDescent="0.35">
       <c r="A30" s="3" t="s">
         <v>87</v>
       </c>
@@ -7932,7 +7932,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:36" ht="18" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:36" ht="18" x14ac:dyDescent="0.35">
       <c r="A31" s="3" t="s">
         <v>88</v>
       </c>
@@ -8012,7 +8012,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:36" ht="18" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:36" ht="18" x14ac:dyDescent="0.35">
       <c r="A32" s="3" t="s">
         <v>89</v>
       </c>
@@ -8092,7 +8092,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:26" ht="18" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:26" ht="18" x14ac:dyDescent="0.35">
       <c r="A33" s="3" t="s">
         <v>90</v>
       </c>
@@ -8172,7 +8172,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:26" ht="18" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:26" ht="18" x14ac:dyDescent="0.35">
       <c r="A34" s="3" t="s">
         <v>91</v>
       </c>
@@ -8252,7 +8252,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:26" ht="18" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:26" ht="18" x14ac:dyDescent="0.35">
       <c r="A35" s="3" t="s">
         <v>92</v>
       </c>
@@ -8332,7 +8332,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:26" ht="18" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:26" ht="18" x14ac:dyDescent="0.35">
       <c r="A36" s="3" t="s">
         <v>93</v>
       </c>
@@ -8412,7 +8412,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:26" ht="18" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:26" ht="18" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
         <v>94</v>
       </c>
@@ -8492,7 +8492,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:26" ht="18" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:26" ht="18" x14ac:dyDescent="0.35">
       <c r="A38" s="3" t="s">
         <v>95</v>
       </c>
@@ -8572,7 +8572,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:26" ht="18" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:26" ht="18" x14ac:dyDescent="0.35">
       <c r="A39" s="3" t="s">
         <v>96</v>
       </c>
@@ -8652,7 +8652,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:26" ht="18" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:26" ht="18" x14ac:dyDescent="0.35">
       <c r="A40" s="3" t="s">
         <v>97</v>
       </c>
@@ -8732,7 +8732,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:26" ht="18" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:26" ht="18" x14ac:dyDescent="0.35">
       <c r="A41" s="3" t="s">
         <v>98</v>
       </c>
@@ -8812,7 +8812,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:26" ht="18" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:26" ht="18" x14ac:dyDescent="0.35">
       <c r="A42" s="3" t="s">
         <v>99</v>
       </c>
@@ -8892,7 +8892,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:26" ht="18" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:26" ht="18" x14ac:dyDescent="0.35">
       <c r="A43" s="3" t="s">
         <v>100</v>
       </c>
@@ -8972,7 +8972,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:26" ht="18" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:26" ht="18" x14ac:dyDescent="0.35">
       <c r="A44" s="3" t="s">
         <v>101</v>
       </c>
@@ -9052,7 +9052,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:26" ht="18" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:26" ht="18" x14ac:dyDescent="0.35">
       <c r="A45" s="3" t="s">
         <v>102</v>
       </c>
@@ -9132,7 +9132,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="1:26" ht="18" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:26" ht="18" x14ac:dyDescent="0.35">
       <c r="A46" s="3" t="s">
         <v>103</v>
       </c>
@@ -9212,7 +9212,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="1:26" ht="18" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:26" ht="18" x14ac:dyDescent="0.35">
       <c r="A47" s="3" t="s">
         <v>104</v>
       </c>
@@ -9292,7 +9292,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:26" ht="18" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:26" ht="18" x14ac:dyDescent="0.35">
       <c r="A48" s="3" t="s">
         <v>105</v>
       </c>
@@ -9372,7 +9372,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:26" ht="18" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:26" ht="18" x14ac:dyDescent="0.35">
       <c r="A49" s="3" t="s">
         <v>106</v>
       </c>
@@ -9452,7 +9452,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:26" ht="18" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:26" ht="18" x14ac:dyDescent="0.35">
       <c r="A50" s="3" t="s">
         <v>107</v>
       </c>
@@ -9532,7 +9532,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="1:26" ht="18" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:26" ht="18" x14ac:dyDescent="0.35">
       <c r="A51" s="3" t="s">
         <v>108</v>
       </c>
@@ -9612,7 +9612,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="1:26" ht="18" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:26" ht="18" x14ac:dyDescent="0.35">
       <c r="A52" s="3" t="s">
         <v>109</v>
       </c>
@@ -9692,7 +9692,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:26" ht="18" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:26" ht="18" x14ac:dyDescent="0.35">
       <c r="A53" s="3" t="s">
         <v>110</v>
       </c>
@@ -9772,7 +9772,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:26" ht="18" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:26" ht="18" x14ac:dyDescent="0.35">
       <c r="A55" s="3" t="s">
         <v>70</v>
       </c>
@@ -9852,7 +9852,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="56" spans="1:26" ht="18" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:26" ht="18" x14ac:dyDescent="0.35">
       <c r="A56" s="3" t="s">
         <v>86</v>
       </c>
@@ -9932,7 +9932,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:26" ht="18" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:26" ht="18" x14ac:dyDescent="0.35">
       <c r="A57" s="3" t="s">
         <v>87</v>
       </c>
@@ -10012,7 +10012,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="1:26" ht="18" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:26" ht="18" x14ac:dyDescent="0.35">
       <c r="A58" s="3" t="s">
         <v>88</v>
       </c>
@@ -10092,7 +10092,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="1:26" ht="18" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:26" ht="18" x14ac:dyDescent="0.35">
       <c r="A59" s="3" t="s">
         <v>89</v>
       </c>
@@ -10172,7 +10172,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="1:26" ht="18" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:26" ht="18" x14ac:dyDescent="0.35">
       <c r="A60" s="3" t="s">
         <v>90</v>
       </c>
@@ -10252,7 +10252,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="1:26" ht="18" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:26" ht="18" x14ac:dyDescent="0.35">
       <c r="A61" s="3" t="s">
         <v>91</v>
       </c>
@@ -10332,7 +10332,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="62" spans="1:26" ht="18" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:26" ht="18" x14ac:dyDescent="0.35">
       <c r="A62" s="3" t="s">
         <v>92</v>
       </c>
@@ -10412,7 +10412,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="1:26" ht="18" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:26" ht="18" x14ac:dyDescent="0.35">
       <c r="A63" s="3" t="s">
         <v>93</v>
       </c>
@@ -10492,7 +10492,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="1:26" ht="18" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:26" ht="18" x14ac:dyDescent="0.35">
       <c r="A64" s="3" t="s">
         <v>94</v>
       </c>
@@ -10572,7 +10572,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="65" spans="1:26" ht="18" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:26" ht="18" x14ac:dyDescent="0.35">
       <c r="A65" s="3" t="s">
         <v>95</v>
       </c>
@@ -10652,7 +10652,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="1:26" ht="18" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:26" ht="18" x14ac:dyDescent="0.35">
       <c r="A66" s="3" t="s">
         <v>96</v>
       </c>
@@ -10732,7 +10732,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="1:26" ht="18" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:26" ht="18" x14ac:dyDescent="0.35">
       <c r="A67" s="3" t="s">
         <v>97</v>
       </c>
@@ -10812,7 +10812,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="68" spans="1:26" ht="18" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:26" ht="18" x14ac:dyDescent="0.35">
       <c r="A68" s="3" t="s">
         <v>98</v>
       </c>
@@ -10892,7 +10892,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="1:26" ht="18" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:26" ht="18" x14ac:dyDescent="0.35">
       <c r="A69" s="3" t="s">
         <v>99</v>
       </c>
@@ -10972,7 +10972,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="70" spans="1:26" ht="18" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:26" ht="18" x14ac:dyDescent="0.35">
       <c r="A70" s="3" t="s">
         <v>100</v>
       </c>
@@ -11052,7 +11052,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="71" spans="1:26" ht="18" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:26" ht="18" x14ac:dyDescent="0.35">
       <c r="A71" s="3" t="s">
         <v>101</v>
       </c>
@@ -11132,7 +11132,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="72" spans="1:26" ht="18" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:26" ht="18" x14ac:dyDescent="0.35">
       <c r="A72" s="3" t="s">
         <v>102</v>
       </c>
@@ -11212,7 +11212,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="1:26" ht="18" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:26" ht="18" x14ac:dyDescent="0.35">
       <c r="A73" s="3" t="s">
         <v>103</v>
       </c>
@@ -11292,7 +11292,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="74" spans="1:26" ht="18" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:26" ht="18" x14ac:dyDescent="0.35">
       <c r="A74" s="3" t="s">
         <v>104</v>
       </c>
@@ -11372,7 +11372,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="75" spans="1:26" ht="18" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:26" ht="18" x14ac:dyDescent="0.35">
       <c r="A75" s="3" t="s">
         <v>105</v>
       </c>
@@ -11452,7 +11452,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="1:26" ht="18" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:26" ht="18" x14ac:dyDescent="0.35">
       <c r="A76" s="3" t="s">
         <v>106</v>
       </c>
@@ -11532,7 +11532,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="77" spans="1:26" ht="18" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:26" ht="18" x14ac:dyDescent="0.35">
       <c r="A77" s="3" t="s">
         <v>107</v>
       </c>
@@ -11612,7 +11612,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="78" spans="1:26" ht="18" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:26" ht="18" x14ac:dyDescent="0.35">
       <c r="A78" s="3" t="s">
         <v>108</v>
       </c>
@@ -11692,7 +11692,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="79" spans="1:26" ht="18" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:26" ht="18" x14ac:dyDescent="0.35">
       <c r="A79" s="3" t="s">
         <v>109</v>
       </c>
@@ -11772,7 +11772,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="1:26" ht="18" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:26" ht="18" x14ac:dyDescent="0.35">
       <c r="A80" s="3" t="s">
         <v>110</v>
       </c>
@@ -11863,19 +11863,19 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B2D18B3-28BF-45AD-9B1B-4433234722D1}">
   <dimension ref="A1:J26"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="80.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.7265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.54296875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="37.26953125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.36328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.1796875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="80.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="37.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -11903,7 +11903,7 @@
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
     </row>
-    <row r="2" spans="1:10" ht="18" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A2" s="3">
         <v>5</v>
       </c>
@@ -11931,7 +11931,7 @@
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
     </row>
-    <row r="3" spans="1:10" ht="18" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -11959,7 +11959,7 @@
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
     </row>
-    <row r="4" spans="1:10" ht="18" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A4" s="3">
         <v>6</v>
       </c>
@@ -11987,7 +11987,7 @@
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
     </row>
-    <row r="5" spans="1:10" ht="18" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A5" s="3">
         <v>1</v>
       </c>
@@ -12015,7 +12015,7 @@
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
     </row>
-    <row r="6" spans="1:10" ht="18" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>19</v>
       </c>
@@ -12043,7 +12043,7 @@
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
     </row>
-    <row r="7" spans="1:10" ht="18" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>3</v>
       </c>
@@ -12071,7 +12071,7 @@
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
     </row>
-    <row r="8" spans="1:10" ht="18" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>12</v>
       </c>
@@ -12099,7 +12099,7 @@
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
     </row>
-    <row r="9" spans="1:10" ht="18" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>17</v>
       </c>
@@ -12127,7 +12127,7 @@
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
     </row>
-    <row r="10" spans="1:10" ht="18" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>4</v>
       </c>
@@ -12155,7 +12155,7 @@
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
     </row>
-    <row r="11" spans="1:10" ht="18" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>7</v>
       </c>
@@ -12183,7 +12183,7 @@
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
     </row>
-    <row r="12" spans="1:10" ht="18" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>24</v>
       </c>
@@ -12211,7 +12211,7 @@
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
     </row>
-    <row r="13" spans="1:10" ht="18" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>10</v>
       </c>
@@ -12239,7 +12239,7 @@
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -12251,7 +12251,7 @@
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -12263,7 +12263,7 @@
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -12275,7 +12275,7 @@
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
@@ -12286,7 +12286,7 @@
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -12298,7 +12298,7 @@
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -12310,7 +12310,7 @@
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -12322,7 +12322,7 @@
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -12334,7 +12334,7 @@
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -12346,7 +12346,7 @@
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -12358,7 +12358,7 @@
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -12370,7 +12370,7 @@
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -12382,7 +12382,7 @@
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
